--- a/Data/EXCEL/Transfer/salemon/202208/6606-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6606-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5A41A4-0034-4484-90BA-56C2AA40D8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94513084-57AB-4DC4-B472-C7E8A7FECEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6606-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,16 +1226,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q154"/>
+  <dimension ref="A1:Q155"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="7" width="11.25" customWidth="1"/>
-    <col min="8" max="14" width="9.875" customWidth="1"/>
-    <col min="15" max="15" width="9.375" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1380,1703 +1388,1703 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="C5" s="7">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="D5" s="7">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="E5" s="7">
-        <v>25.6</v>
+        <v>25.95</v>
       </c>
       <c r="F5" s="8">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="8">
-        <v>-0.37</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H5" s="9">
-        <v>0.82899999999999996</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="I5" s="8">
-        <v>-8.81</v>
-      </c>
-      <c r="J5" s="10">
-        <v>6.01</v>
+        <v>10</v>
+      </c>
+      <c r="J5" s="8">
+        <v>32.6</v>
       </c>
       <c r="K5" s="9">
-        <v>5.43</v>
-      </c>
-      <c r="L5" s="10">
-        <v>4.0199999999999996</v>
+        <v>6.34</v>
+      </c>
+      <c r="L5" s="8">
+        <v>7.35</v>
       </c>
       <c r="M5" s="9">
-        <v>0.82899999999999996</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="N5" s="8">
-        <v>-8.81</v>
-      </c>
-      <c r="O5" s="10">
-        <v>6.01</v>
+        <v>10</v>
+      </c>
+      <c r="O5" s="8">
+        <v>32.6</v>
       </c>
       <c r="P5" s="9">
-        <v>5.43</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>4.0199999999999996</v>
+        <v>6.34</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>7.35</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="C6" s="7">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="D6" s="7">
-        <v>28.9</v>
+        <v>27.5</v>
       </c>
       <c r="E6" s="7">
         <v>25.6</v>
       </c>
-      <c r="F6" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="G6" s="8">
-        <v>-6.64</v>
+      <c r="F6" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-0.37</v>
       </c>
       <c r="H6" s="9">
-        <v>0.90900000000000003</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="I6" s="10">
-        <v>7.63</v>
+        <v>-8.81</v>
       </c>
       <c r="J6" s="8">
-        <v>-1.28</v>
+        <v>6.01</v>
       </c>
       <c r="K6" s="9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L6" s="10">
-        <v>3.67</v>
+        <v>5.43</v>
+      </c>
+      <c r="L6" s="8">
+        <v>4.0199999999999996</v>
       </c>
       <c r="M6" s="9">
-        <v>0.90900000000000003</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="N6" s="10">
-        <v>7.63</v>
+        <v>-8.81</v>
       </c>
       <c r="O6" s="8">
-        <v>-1.28</v>
+        <v>6.01</v>
       </c>
       <c r="P6" s="9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>3.67</v>
+        <v>5.43</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>4.0199999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="C7" s="7">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="D7" s="7">
-        <v>29.05</v>
+        <v>28.9</v>
       </c>
       <c r="E7" s="7">
-        <v>27.85</v>
-      </c>
-      <c r="F7" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-0.69</v>
+        <v>25.6</v>
+      </c>
+      <c r="F7" s="10">
+        <v>-1.9</v>
+      </c>
+      <c r="G7" s="10">
+        <v>-6.64</v>
       </c>
       <c r="H7" s="9">
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="I7" s="10">
-        <v>18.3</v>
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="I7" s="8">
+        <v>7.63</v>
       </c>
       <c r="J7" s="10">
-        <v>3.13</v>
+        <v>-1.28</v>
       </c>
       <c r="K7" s="9">
-        <v>3.69</v>
-      </c>
-      <c r="L7" s="10">
-        <v>4.97</v>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L7" s="8">
+        <v>3.67</v>
       </c>
       <c r="M7" s="9">
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="N7" s="10">
-        <v>18.3</v>
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="N7" s="8">
+        <v>7.63</v>
       </c>
       <c r="O7" s="10">
-        <v>3.13</v>
+        <v>-1.28</v>
       </c>
       <c r="P7" s="9">
-        <v>3.69</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>4.97</v>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>3.67</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>27.35</v>
+        <v>28.8</v>
       </c>
       <c r="C8" s="7">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D8" s="7">
-        <v>30.4</v>
+        <v>29.05</v>
       </c>
       <c r="E8" s="7">
-        <v>27.15</v>
+        <v>27.85</v>
       </c>
       <c r="F8" s="10">
-        <v>1.45</v>
+        <v>-0.2</v>
       </c>
       <c r="G8" s="10">
-        <v>5.3</v>
+        <v>-0.69</v>
       </c>
       <c r="H8" s="9">
-        <v>0.71399999999999997</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="I8" s="8">
-        <v>-32.799999999999997</v>
+        <v>18.3</v>
       </c>
       <c r="J8" s="8">
-        <v>-10.7</v>
+        <v>3.13</v>
       </c>
       <c r="K8" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="L8" s="10">
-        <v>5.52</v>
+        <v>3.69</v>
+      </c>
+      <c r="L8" s="8">
+        <v>4.97</v>
       </c>
       <c r="M8" s="9">
-        <v>0.71399999999999997</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="N8" s="8">
-        <v>-32.799999999999997</v>
+        <v>18.3</v>
       </c>
       <c r="O8" s="8">
-        <v>-10.7</v>
+        <v>3.13</v>
       </c>
       <c r="P8" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>5.52</v>
+        <v>3.69</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>4.97</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
+        <v>27.35</v>
+      </c>
+      <c r="C9" s="7">
+        <v>28.8</v>
+      </c>
+      <c r="D9" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="E9" s="7">
         <v>27.15</v>
       </c>
-      <c r="C9" s="7">
-        <v>27.35</v>
-      </c>
-      <c r="D9" s="7">
-        <v>27.65</v>
-      </c>
-      <c r="E9" s="7">
-        <v>26.8</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0.74</v>
+      <c r="F9" s="8">
+        <v>1.45</v>
+      </c>
+      <c r="G9" s="8">
+        <v>5.3</v>
       </c>
       <c r="H9" s="9">
-        <v>1.06</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="I9" s="10">
-        <v>147.19999999999999</v>
+        <v>-32.799999999999997</v>
       </c>
       <c r="J9" s="10">
-        <v>22.7</v>
+        <v>-10.7</v>
       </c>
       <c r="K9" s="9">
-        <v>2.13</v>
-      </c>
-      <c r="L9" s="10">
-        <v>12.4</v>
+        <v>2.85</v>
+      </c>
+      <c r="L9" s="8">
+        <v>5.52</v>
       </c>
       <c r="M9" s="9">
-        <v>1.06</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="N9" s="10">
-        <v>147.19999999999999</v>
+        <v>-32.799999999999997</v>
       </c>
       <c r="O9" s="10">
-        <v>22.7</v>
+        <v>-10.7</v>
       </c>
       <c r="P9" s="9">
-        <v>2.13</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>12.4</v>
+        <v>2.85</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>5.52</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>27.95</v>
+        <v>27.15</v>
       </c>
       <c r="C10" s="7">
-        <v>27.15</v>
+        <v>27.35</v>
       </c>
       <c r="D10" s="7">
-        <v>27.95</v>
+        <v>27.65</v>
       </c>
       <c r="E10" s="7">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="F10" s="8">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="8">
-        <v>-2.86</v>
+        <v>0.74</v>
       </c>
       <c r="H10" s="9">
-        <v>0.43</v>
+        <v>1.06</v>
       </c>
       <c r="I10" s="8">
-        <v>-32.9</v>
-      </c>
-      <c r="J10" s="10">
-        <v>49.6</v>
+        <v>147.19999999999999</v>
+      </c>
+      <c r="J10" s="8">
+        <v>22.7</v>
       </c>
       <c r="K10" s="9">
-        <v>1.07</v>
-      </c>
-      <c r="L10" s="10">
-        <v>3.7</v>
+        <v>2.13</v>
+      </c>
+      <c r="L10" s="8">
+        <v>12.4</v>
       </c>
       <c r="M10" s="9">
-        <v>0.43</v>
+        <v>1.06</v>
       </c>
       <c r="N10" s="8">
-        <v>-32.9</v>
-      </c>
-      <c r="O10" s="10">
-        <v>49.6</v>
+        <v>147.19999999999999</v>
+      </c>
+      <c r="O10" s="8">
+        <v>22.7</v>
       </c>
       <c r="P10" s="9">
-        <v>1.07</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>3.7</v>
+        <v>2.13</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>12.4</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>27.1</v>
+        <v>27.95</v>
       </c>
       <c r="C11" s="7">
-        <v>27.95</v>
+        <v>27.15</v>
       </c>
       <c r="D11" s="7">
         <v>27.95</v>
       </c>
       <c r="E11" s="7">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="F11" s="10">
-        <v>0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="G11" s="10">
-        <v>3.14</v>
+        <v>-2.86</v>
       </c>
       <c r="H11" s="9">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="I11" s="10">
-        <v>12.9</v>
+        <v>-32.9</v>
       </c>
       <c r="J11" s="8">
-        <v>-14</v>
+        <v>49.6</v>
       </c>
       <c r="K11" s="9">
-        <v>0.64</v>
+        <v>1.07</v>
       </c>
       <c r="L11" s="8">
-        <v>-14</v>
+        <v>3.7</v>
       </c>
       <c r="M11" s="9">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="N11" s="10">
-        <v>12.9</v>
+        <v>-32.9</v>
       </c>
       <c r="O11" s="8">
-        <v>-14</v>
+        <v>49.6</v>
       </c>
       <c r="P11" s="9">
-        <v>0.64</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" s="8">
-        <v>-14</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="C12" s="7">
-        <v>27.1</v>
+        <v>27.95</v>
       </c>
       <c r="D12" s="7">
-        <v>28.05</v>
+        <v>27.95</v>
       </c>
       <c r="E12" s="7">
-        <v>25.4</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="10">
-        <v>1.1200000000000001</v>
+        <v>26.4</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="G12" s="8">
+        <v>3.14</v>
       </c>
       <c r="H12" s="9">
-        <v>0.56699999999999995</v>
+        <v>0.64</v>
       </c>
       <c r="I12" s="8">
-        <v>-31.2</v>
-      </c>
-      <c r="J12" s="8">
-        <v>-29.9</v>
+        <v>12.9</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-14</v>
       </c>
       <c r="K12" s="9">
-        <v>8.74</v>
+        <v>0.64</v>
       </c>
       <c r="L12" s="10">
-        <v>23.4</v>
+        <v>-14</v>
       </c>
       <c r="M12" s="9">
-        <v>0.56699999999999995</v>
+        <v>0.64</v>
       </c>
       <c r="N12" s="8">
-        <v>-31.2</v>
-      </c>
-      <c r="O12" s="8">
-        <v>-29.9</v>
+        <v>12.9</v>
+      </c>
+      <c r="O12" s="10">
+        <v>-14</v>
       </c>
       <c r="P12" s="9">
-        <v>8.74</v>
+        <v>0.64</v>
       </c>
       <c r="Q12" s="10">
-        <v>23.4</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="C13" s="7">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="D13" s="7">
-        <v>27.2</v>
+        <v>28.05</v>
       </c>
       <c r="E13" s="7">
-        <v>26.15</v>
+        <v>25.4</v>
       </c>
       <c r="F13" s="8">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G13" s="8">
-        <v>-0.74</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H13" s="9">
-        <v>0.82299999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="I13" s="10">
-        <v>19.7</v>
+        <v>-31.2</v>
       </c>
       <c r="J13" s="10">
-        <v>41.3</v>
+        <v>-29.9</v>
       </c>
       <c r="K13" s="9">
-        <v>8.17</v>
-      </c>
-      <c r="L13" s="10">
-        <v>30.3</v>
+        <v>8.74</v>
+      </c>
+      <c r="L13" s="8">
+        <v>23.4</v>
       </c>
       <c r="M13" s="9">
-        <v>0.82299999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="N13" s="10">
-        <v>19.7</v>
+        <v>-31.2</v>
       </c>
       <c r="O13" s="10">
-        <v>41.3</v>
+        <v>-29.9</v>
       </c>
       <c r="P13" s="9">
-        <v>8.17</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>30.3</v>
+        <v>8.74</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>23.4</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D14" s="7">
         <v>27.2</v>
       </c>
       <c r="E14" s="7">
-        <v>26.7</v>
-      </c>
-      <c r="F14" s="8">
+        <v>26.15</v>
+      </c>
+      <c r="F14" s="10">
         <v>-0.2</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="10">
         <v>-0.74</v>
       </c>
       <c r="H14" s="9">
-        <v>0.68799999999999994</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="I14" s="8">
-        <v>-8.9600000000000009</v>
+        <v>19.7</v>
       </c>
       <c r="J14" s="8">
-        <v>-3.88</v>
+        <v>41.3</v>
       </c>
       <c r="K14" s="9">
-        <v>7.35</v>
-      </c>
-      <c r="L14" s="10">
-        <v>29.2</v>
+        <v>8.17</v>
+      </c>
+      <c r="L14" s="8">
+        <v>30.3</v>
       </c>
       <c r="M14" s="9">
-        <v>0.68799999999999994</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="N14" s="8">
-        <v>-8.9600000000000009</v>
+        <v>19.7</v>
       </c>
       <c r="O14" s="8">
-        <v>-3.88</v>
+        <v>41.3</v>
       </c>
       <c r="P14" s="9">
-        <v>7.35</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>29.2</v>
+        <v>8.17</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>30.3</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="C15" s="7">
+        <v>27</v>
+      </c>
+      <c r="D15" s="7">
         <v>27.2</v>
       </c>
-      <c r="D15" s="7">
-        <v>27.35</v>
-      </c>
       <c r="E15" s="7">
-        <v>26.25</v>
+        <v>26.7</v>
       </c>
       <c r="F15" s="10">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G15" s="10">
-        <v>0.37</v>
+        <v>-0.74</v>
       </c>
       <c r="H15" s="9">
-        <v>0.75600000000000001</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="I15" s="10">
-        <v>9.84</v>
+        <v>-8.9600000000000009</v>
       </c>
       <c r="J15" s="10">
-        <v>15.1</v>
+        <v>-3.88</v>
       </c>
       <c r="K15" s="9">
-        <v>6.66</v>
-      </c>
-      <c r="L15" s="10">
-        <v>33.9</v>
+        <v>7.35</v>
+      </c>
+      <c r="L15" s="8">
+        <v>29.2</v>
       </c>
       <c r="M15" s="9">
-        <v>0.75600000000000001</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="N15" s="10">
-        <v>9.84</v>
+        <v>-8.9600000000000009</v>
       </c>
       <c r="O15" s="10">
-        <v>15.1</v>
+        <v>-3.88</v>
       </c>
       <c r="P15" s="9">
-        <v>6.66</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>33.9</v>
+        <v>7.35</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>29.2</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>27.55</v>
+        <v>27.1</v>
       </c>
       <c r="C16" s="7">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D16" s="7">
-        <v>27.6</v>
+        <v>27.35</v>
       </c>
       <c r="E16" s="7">
-        <v>26.4</v>
+        <v>26.25</v>
       </c>
       <c r="F16" s="8">
-        <v>-0.45</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="8">
-        <v>-1.63</v>
+        <v>0.37</v>
       </c>
       <c r="H16" s="9">
-        <v>0.68799999999999994</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="I16" s="8">
-        <v>-12</v>
-      </c>
-      <c r="J16" s="10">
-        <v>42.8</v>
+        <v>9.84</v>
+      </c>
+      <c r="J16" s="8">
+        <v>15.1</v>
       </c>
       <c r="K16" s="9">
-        <v>5.91</v>
-      </c>
-      <c r="L16" s="10">
-        <v>36.799999999999997</v>
+        <v>6.66</v>
+      </c>
+      <c r="L16" s="8">
+        <v>33.9</v>
       </c>
       <c r="M16" s="9">
-        <v>0.68799999999999994</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="N16" s="8">
-        <v>-12</v>
-      </c>
-      <c r="O16" s="10">
-        <v>42.8</v>
+        <v>9.84</v>
+      </c>
+      <c r="O16" s="8">
+        <v>15.1</v>
       </c>
       <c r="P16" s="9">
-        <v>5.91</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>36.799999999999997</v>
+        <v>6.66</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>33.9</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>29.3</v>
+        <v>27.55</v>
       </c>
       <c r="C17" s="7">
-        <v>27.55</v>
+        <v>27.1</v>
       </c>
       <c r="D17" s="7">
-        <v>30</v>
+        <v>27.6</v>
       </c>
       <c r="E17" s="7">
-        <v>26.85</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-1.75</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-5.97</v>
+        <v>26.4</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-1.63</v>
       </c>
       <c r="H17" s="9">
-        <v>0.78200000000000003</v>
-      </c>
-      <c r="I17" s="8">
-        <v>-15.1</v>
-      </c>
-      <c r="J17" s="10">
-        <v>15.6</v>
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="I17" s="10">
+        <v>-12</v>
+      </c>
+      <c r="J17" s="8">
+        <v>42.8</v>
       </c>
       <c r="K17" s="9">
-        <v>5.22</v>
-      </c>
-      <c r="L17" s="10">
-        <v>36</v>
+        <v>5.91</v>
+      </c>
+      <c r="L17" s="8">
+        <v>36.799999999999997</v>
       </c>
       <c r="M17" s="9">
-        <v>0.78200000000000003</v>
-      </c>
-      <c r="N17" s="8">
-        <v>-15.1</v>
-      </c>
-      <c r="O17" s="10">
-        <v>15.6</v>
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="N17" s="10">
+        <v>-12</v>
+      </c>
+      <c r="O17" s="8">
+        <v>42.8</v>
       </c>
       <c r="P17" s="9">
-        <v>5.22</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>36</v>
+        <v>5.91</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="C18" s="7">
-        <v>29.3</v>
+        <v>27.55</v>
       </c>
       <c r="D18" s="7">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="E18" s="7">
-        <v>27.45</v>
+        <v>26.85</v>
       </c>
       <c r="F18" s="10">
-        <v>1.3</v>
+        <v>-1.75</v>
       </c>
       <c r="G18" s="10">
-        <v>4.6399999999999997</v>
+        <v>-5.97</v>
       </c>
       <c r="H18" s="9">
-        <v>0.92100000000000004</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="I18" s="10">
-        <v>12.4</v>
-      </c>
-      <c r="J18" s="10">
-        <v>18.2</v>
+        <v>-15.1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>15.6</v>
       </c>
       <c r="K18" s="9">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="L18" s="10">
-        <v>40.4</v>
+        <v>5.22</v>
+      </c>
+      <c r="L18" s="8">
+        <v>36</v>
       </c>
       <c r="M18" s="9">
-        <v>0.92100000000000004</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="N18" s="10">
-        <v>12.4</v>
-      </c>
-      <c r="O18" s="10">
-        <v>18.2</v>
+        <v>-15.1</v>
+      </c>
+      <c r="O18" s="8">
+        <v>15.6</v>
       </c>
       <c r="P18" s="9">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>40.4</v>
+        <v>5.22</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
+        <v>28</v>
+      </c>
+      <c r="C19" s="7">
+        <v>29.3</v>
+      </c>
+      <c r="D19" s="7">
         <v>29.6</v>
       </c>
-      <c r="C19" s="7">
-        <v>28</v>
-      </c>
-      <c r="D19" s="7">
-        <v>29.8</v>
-      </c>
       <c r="E19" s="7">
-        <v>25.4</v>
+        <v>27.45</v>
       </c>
       <c r="F19" s="8">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G19" s="8">
-        <v>-5.41</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="H19" s="9">
-        <v>0.81899999999999995</v>
-      </c>
-      <c r="I19" s="10">
-        <v>2.44</v>
-      </c>
-      <c r="J19" s="10">
-        <v>29.3</v>
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="I19" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="J19" s="8">
+        <v>18.2</v>
       </c>
       <c r="K19" s="9">
-        <v>3.52</v>
-      </c>
-      <c r="L19" s="10">
-        <v>47.7</v>
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="L19" s="8">
+        <v>40.4</v>
       </c>
       <c r="M19" s="9">
-        <v>0.81899999999999995</v>
-      </c>
-      <c r="N19" s="10">
-        <v>2.44</v>
-      </c>
-      <c r="O19" s="10">
-        <v>29.3</v>
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="N19" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="O19" s="8">
+        <v>18.2</v>
       </c>
       <c r="P19" s="9">
-        <v>3.52</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>47.7</v>
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>40.4</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>26</v>
+        <v>29.6</v>
       </c>
       <c r="C20" s="7">
-        <v>29.6</v>
+        <v>28</v>
       </c>
       <c r="D20" s="7">
-        <v>31.45</v>
+        <v>29.8</v>
       </c>
       <c r="E20" s="7">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="F20" s="10">
-        <v>3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="G20" s="10">
-        <v>13.85</v>
+        <v>-5.41</v>
       </c>
       <c r="H20" s="9">
-        <v>0.8</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="I20" s="8">
-        <v>-7.64</v>
-      </c>
-      <c r="J20" s="10">
-        <v>24.8</v>
+        <v>2.44</v>
+      </c>
+      <c r="J20" s="8">
+        <v>29.3</v>
       </c>
       <c r="K20" s="9">
-        <v>2.7</v>
-      </c>
-      <c r="L20" s="10">
-        <v>54.4</v>
+        <v>3.52</v>
+      </c>
+      <c r="L20" s="8">
+        <v>47.7</v>
       </c>
       <c r="M20" s="9">
-        <v>0.8</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="N20" s="8">
-        <v>-7.64</v>
-      </c>
-      <c r="O20" s="10">
-        <v>24.8</v>
+        <v>2.44</v>
+      </c>
+      <c r="O20" s="8">
+        <v>29.3</v>
       </c>
       <c r="P20" s="9">
-        <v>2.7</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>54.4</v>
+        <v>3.52</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>47.7</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>24.45</v>
+        <v>26</v>
       </c>
       <c r="C21" s="7">
-        <v>26</v>
+        <v>29.6</v>
       </c>
       <c r="D21" s="7">
-        <v>27.7</v>
+        <v>31.45</v>
       </c>
       <c r="E21" s="7">
-        <v>22.75</v>
-      </c>
-      <c r="F21" s="10">
-        <v>1.55</v>
-      </c>
-      <c r="G21" s="10">
-        <v>6.34</v>
+        <v>25.5</v>
+      </c>
+      <c r="F21" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G21" s="8">
+        <v>13.85</v>
       </c>
       <c r="H21" s="9">
-        <v>0.86599999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="I21" s="10">
-        <v>201.4</v>
-      </c>
-      <c r="J21" s="10">
-        <v>84.2</v>
+        <v>-7.64</v>
+      </c>
+      <c r="J21" s="8">
+        <v>24.8</v>
       </c>
       <c r="K21" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="L21" s="10">
-        <v>71.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="L21" s="8">
+        <v>54.4</v>
       </c>
       <c r="M21" s="9">
-        <v>0.86599999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="N21" s="10">
-        <v>201.4</v>
-      </c>
-      <c r="O21" s="10">
-        <v>84.2</v>
+        <v>-7.64</v>
+      </c>
+      <c r="O21" s="8">
+        <v>24.8</v>
       </c>
       <c r="P21" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>71.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>54.4</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>22</v>
+        <v>24.45</v>
       </c>
       <c r="C22" s="7">
-        <v>24.45</v>
+        <v>26</v>
       </c>
       <c r="D22" s="7">
-        <v>25.6</v>
+        <v>27.7</v>
       </c>
       <c r="E22" s="7">
-        <v>22</v>
-      </c>
-      <c r="F22" s="10">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="G22" s="10">
-        <v>11.14</v>
+        <v>22.75</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="G22" s="8">
+        <v>6.34</v>
       </c>
       <c r="H22" s="9">
-        <v>0.28699999999999998</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="I22" s="8">
-        <v>-61.4</v>
-      </c>
-      <c r="J22" s="10">
-        <v>81.599999999999994</v>
+        <v>201.4</v>
+      </c>
+      <c r="J22" s="8">
+        <v>84.2</v>
       </c>
       <c r="K22" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="L22" s="10">
-        <v>62.1</v>
+        <v>1.9</v>
+      </c>
+      <c r="L22" s="8">
+        <v>71.5</v>
       </c>
       <c r="M22" s="9">
-        <v>0.28699999999999998</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="N22" s="8">
-        <v>-61.4</v>
-      </c>
-      <c r="O22" s="10">
-        <v>81.599999999999994</v>
+        <v>201.4</v>
+      </c>
+      <c r="O22" s="8">
+        <v>84.2</v>
       </c>
       <c r="P22" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>62.1</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>71.5</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" s="7">
-        <v>22</v>
+        <v>24.45</v>
       </c>
       <c r="D23" s="7">
-        <v>24.75</v>
+        <v>25.6</v>
       </c>
       <c r="E23" s="7">
         <v>22</v>
       </c>
       <c r="F23" s="8">
-        <v>-2</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G23" s="8">
-        <v>-8.33</v>
+        <v>11.14</v>
       </c>
       <c r="H23" s="9">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="I23" s="8">
-        <v>-7.93</v>
-      </c>
-      <c r="J23" s="10">
-        <v>55.7</v>
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="I23" s="10">
+        <v>-61.4</v>
+      </c>
+      <c r="J23" s="8">
+        <v>81.599999999999994</v>
       </c>
       <c r="K23" s="9">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="L23" s="10">
-        <v>55.7</v>
+        <v>1.03</v>
+      </c>
+      <c r="L23" s="8">
+        <v>62.1</v>
       </c>
       <c r="M23" s="9">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="N23" s="8">
-        <v>-7.93</v>
-      </c>
-      <c r="O23" s="10">
-        <v>55.7</v>
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="N23" s="10">
+        <v>-61.4</v>
+      </c>
+      <c r="O23" s="8">
+        <v>81.599999999999994</v>
       </c>
       <c r="P23" s="9">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>55.7</v>
+        <v>1.03</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>62.1</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="C24" s="7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D24" s="7">
-        <v>25</v>
+        <v>24.75</v>
       </c>
       <c r="E24" s="7">
-        <v>23.5</v>
-      </c>
-      <c r="F24" s="8">
-        <v>-0.6</v>
-      </c>
-      <c r="G24" s="8">
-        <v>-2.44</v>
+        <v>22</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-2</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-8.33</v>
       </c>
       <c r="H24" s="9">
-        <v>0.80800000000000005</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="I24" s="10">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="J24" s="10">
-        <v>56.9</v>
+        <v>-7.93</v>
+      </c>
+      <c r="J24" s="8">
+        <v>55.7</v>
       </c>
       <c r="K24" s="9">
-        <v>7.08</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="L24" s="8">
-        <v>-3.38</v>
+        <v>55.7</v>
       </c>
       <c r="M24" s="9">
-        <v>0.80800000000000005</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="N24" s="10">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="O24" s="10">
-        <v>56.9</v>
+        <v>-7.93</v>
+      </c>
+      <c r="O24" s="8">
+        <v>55.7</v>
       </c>
       <c r="P24" s="9">
-        <v>7.08</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="Q24" s="8">
-        <v>-3.38</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="C25" s="7">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D25" s="7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="7">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="F25" s="10">
-        <v>0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="G25" s="10">
-        <v>3.8</v>
+        <v>-2.44</v>
       </c>
       <c r="H25" s="9">
-        <v>0.58299999999999996</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="I25" s="8">
-        <v>-18.600000000000001</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="J25" s="8">
-        <v>-4.3</v>
+        <v>56.9</v>
       </c>
       <c r="K25" s="9">
-        <v>6.27</v>
-      </c>
-      <c r="L25" s="8">
-        <v>-7.94</v>
+        <v>7.08</v>
+      </c>
+      <c r="L25" s="10">
+        <v>-3.38</v>
       </c>
       <c r="M25" s="9">
-        <v>0.58299999999999996</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="N25" s="8">
-        <v>-18.600000000000001</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="O25" s="8">
-        <v>-4.3</v>
+        <v>56.9</v>
       </c>
       <c r="P25" s="9">
-        <v>6.27</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>-7.94</v>
+        <v>7.08</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>-3.38</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>26.5</v>
+        <v>23.7</v>
       </c>
       <c r="C26" s="7">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="D26" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="7">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="F26" s="8">
-        <v>-2.8</v>
+        <v>0.9</v>
       </c>
       <c r="G26" s="8">
-        <v>-10.57</v>
+        <v>3.8</v>
       </c>
       <c r="H26" s="9">
-        <v>0.71599999999999997</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="I26" s="10">
-        <v>9</v>
+        <v>-18.600000000000001</v>
       </c>
       <c r="J26" s="10">
-        <v>12.4</v>
+        <v>-4.3</v>
       </c>
       <c r="K26" s="9">
-        <v>5.69</v>
-      </c>
-      <c r="L26" s="8">
-        <v>-8.3000000000000007</v>
+        <v>6.27</v>
+      </c>
+      <c r="L26" s="10">
+        <v>-7.94</v>
       </c>
       <c r="M26" s="9">
-        <v>0.71599999999999997</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="N26" s="10">
-        <v>9</v>
+        <v>-18.600000000000001</v>
       </c>
       <c r="O26" s="10">
-        <v>12.4</v>
+        <v>-4.3</v>
       </c>
       <c r="P26" s="9">
-        <v>5.69</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>-8.3000000000000007</v>
+        <v>6.27</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>-7.94</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>29</v>
+        <v>26.5</v>
       </c>
       <c r="C27" s="7">
-        <v>26.5</v>
+        <v>23.7</v>
       </c>
       <c r="D27" s="7">
-        <v>29.1</v>
+        <v>27</v>
       </c>
       <c r="E27" s="7">
-        <v>26</v>
-      </c>
-      <c r="F27" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G27" s="8">
-        <v>-8.6199999999999992</v>
+        <v>23.5</v>
+      </c>
+      <c r="F27" s="10">
+        <v>-2.8</v>
+      </c>
+      <c r="G27" s="10">
+        <v>-10.57</v>
       </c>
       <c r="H27" s="9">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="I27" s="10">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="J27" s="10">
-        <v>12</v>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="I27" s="8">
+        <v>9</v>
+      </c>
+      <c r="J27" s="8">
+        <v>12.4</v>
       </c>
       <c r="K27" s="9">
-        <v>4.97</v>
-      </c>
-      <c r="L27" s="8">
-        <v>-10.7</v>
+        <v>5.69</v>
+      </c>
+      <c r="L27" s="10">
+        <v>-8.3000000000000007</v>
       </c>
       <c r="M27" s="9">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="N27" s="10">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="O27" s="10">
-        <v>12</v>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="N27" s="8">
+        <v>9</v>
+      </c>
+      <c r="O27" s="8">
+        <v>12.4</v>
       </c>
       <c r="P27" s="9">
-        <v>4.97</v>
-      </c>
-      <c r="Q27" s="8">
-        <v>-10.7</v>
+        <v>5.69</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>-8.3000000000000007</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>23.5</v>
+        <v>29</v>
       </c>
       <c r="C28" s="7">
-        <v>29</v>
+        <v>26.5</v>
       </c>
       <c r="D28" s="7">
-        <v>29.45</v>
+        <v>29.1</v>
       </c>
       <c r="E28" s="7">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="F28" s="10">
-        <v>5.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G28" s="10">
-        <v>23.4</v>
+        <v>-8.6199999999999992</v>
       </c>
       <c r="H28" s="9">
-        <v>0.48199999999999998</v>
+        <v>0.65700000000000003</v>
       </c>
       <c r="I28" s="8">
-        <v>-28.8</v>
-      </c>
-      <c r="J28" s="10">
-        <v>23.3</v>
+        <v>36.299999999999997</v>
+      </c>
+      <c r="J28" s="8">
+        <v>12</v>
       </c>
       <c r="K28" s="9">
-        <v>4.32</v>
-      </c>
-      <c r="L28" s="8">
-        <v>-13.3</v>
+        <v>4.97</v>
+      </c>
+      <c r="L28" s="10">
+        <v>-10.7</v>
       </c>
       <c r="M28" s="9">
-        <v>0.48199999999999998</v>
+        <v>0.65700000000000003</v>
       </c>
       <c r="N28" s="8">
-        <v>-28.8</v>
-      </c>
-      <c r="O28" s="10">
-        <v>23.3</v>
+        <v>36.299999999999997</v>
+      </c>
+      <c r="O28" s="8">
+        <v>12</v>
       </c>
       <c r="P28" s="9">
-        <v>4.32</v>
-      </c>
-      <c r="Q28" s="8">
-        <v>-13.3</v>
+        <v>4.97</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>-10.7</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="C29" s="7">
-        <v>23.5</v>
+        <v>29</v>
       </c>
       <c r="D29" s="7">
-        <v>24.4</v>
+        <v>29.45</v>
       </c>
       <c r="E29" s="7">
-        <v>21.8</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="10">
-        <v>6.82</v>
+        <v>22.9</v>
+      </c>
+      <c r="F29" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="G29" s="8">
+        <v>23.4</v>
       </c>
       <c r="H29" s="9">
-        <v>0.67700000000000005</v>
-      </c>
-      <c r="I29" s="8">
-        <v>-13.1</v>
-      </c>
-      <c r="J29" s="10">
-        <v>9.17</v>
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="I29" s="10">
+        <v>-28.8</v>
+      </c>
+      <c r="J29" s="8">
+        <v>23.3</v>
       </c>
       <c r="K29" s="9">
-        <v>3.84</v>
-      </c>
-      <c r="L29" s="8">
-        <v>-16.5</v>
+        <v>4.32</v>
+      </c>
+      <c r="L29" s="10">
+        <v>-13.3</v>
       </c>
       <c r="M29" s="9">
-        <v>0.67700000000000005</v>
-      </c>
-      <c r="N29" s="8">
-        <v>-13.1</v>
-      </c>
-      <c r="O29" s="10">
-        <v>9.17</v>
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="N29" s="10">
+        <v>-28.8</v>
+      </c>
+      <c r="O29" s="8">
+        <v>23.3</v>
       </c>
       <c r="P29" s="9">
-        <v>3.84</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>-16.5</v>
+        <v>4.32</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>-13.3</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="C30" s="7">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="D30" s="7">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="E30" s="7">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F30" s="8">
-        <v>-0.1</v>
+        <v>1.5</v>
       </c>
       <c r="G30" s="8">
-        <v>-0.45</v>
+        <v>6.82</v>
       </c>
       <c r="H30" s="9">
-        <v>0.77900000000000003</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="I30" s="10">
-        <v>23</v>
-      </c>
-      <c r="J30" s="10">
-        <v>9.1300000000000008</v>
+        <v>-13.1</v>
+      </c>
+      <c r="J30" s="8">
+        <v>9.17</v>
       </c>
       <c r="K30" s="9">
-        <v>3.16</v>
-      </c>
-      <c r="L30" s="8">
-        <v>-20.5</v>
+        <v>3.84</v>
+      </c>
+      <c r="L30" s="10">
+        <v>-16.5</v>
       </c>
       <c r="M30" s="9">
-        <v>0.77900000000000003</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="N30" s="10">
-        <v>23</v>
-      </c>
-      <c r="O30" s="10">
-        <v>9.1300000000000008</v>
+        <v>-13.1</v>
+      </c>
+      <c r="O30" s="8">
+        <v>9.17</v>
       </c>
       <c r="P30" s="9">
-        <v>3.16</v>
-      </c>
-      <c r="Q30" s="8">
-        <v>-20.5</v>
+        <v>3.84</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>-16.5</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
         <v>22.1</v>
       </c>
       <c r="C31" s="7">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D31" s="7">
-        <v>22.55</v>
+        <v>23</v>
       </c>
       <c r="E31" s="7">
-        <v>21.15</v>
-      </c>
-      <c r="F31" s="9">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>0</v>
+        <v>21.7</v>
+      </c>
+      <c r="F31" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G31" s="10">
+        <v>-0.45</v>
       </c>
       <c r="H31" s="9">
-        <v>0.63400000000000001</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="I31" s="8">
-        <v>-1.08</v>
+        <v>23</v>
       </c>
       <c r="J31" s="8">
-        <v>-12.7</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="K31" s="9">
-        <v>2.38</v>
-      </c>
-      <c r="L31" s="8">
-        <v>-26.9</v>
+        <v>3.16</v>
+      </c>
+      <c r="L31" s="10">
+        <v>-20.5</v>
       </c>
       <c r="M31" s="9">
-        <v>0.63400000000000001</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="N31" s="8">
-        <v>-1.08</v>
+        <v>23</v>
       </c>
       <c r="O31" s="8">
-        <v>-12.7</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="P31" s="9">
-        <v>2.38</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>-26.9</v>
+        <v>3.16</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>-20.5</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="C32" s="7">
         <v>22.1</v>
       </c>
       <c r="D32" s="7">
-        <v>23</v>
+        <v>22.55</v>
       </c>
       <c r="E32" s="7">
-        <v>20.9</v>
-      </c>
-      <c r="F32" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G32" s="10">
-        <v>5.24</v>
+        <v>21.15</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
       </c>
       <c r="H32" s="9">
-        <v>0.64</v>
+        <v>0.63400000000000001</v>
       </c>
       <c r="I32" s="10">
-        <v>36.299999999999997</v>
+        <v>-1.08</v>
       </c>
       <c r="J32" s="10">
-        <v>31</v>
+        <v>-12.7</v>
       </c>
       <c r="K32" s="9">
-        <v>1.75</v>
-      </c>
-      <c r="L32" s="8">
-        <v>-31</v>
+        <v>2.38</v>
+      </c>
+      <c r="L32" s="10">
+        <v>-26.9</v>
       </c>
       <c r="M32" s="9">
-        <v>0.64</v>
+        <v>0.63400000000000001</v>
       </c>
       <c r="N32" s="10">
-        <v>36.299999999999997</v>
+        <v>-1.08</v>
       </c>
       <c r="O32" s="10">
-        <v>31</v>
+        <v>-12.7</v>
       </c>
       <c r="P32" s="9">
-        <v>1.75</v>
-      </c>
-      <c r="Q32" s="8">
-        <v>-31</v>
+        <v>2.38</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>-26.9</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="C33" s="7">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="D33" s="7">
-        <v>21.99</v>
+        <v>23</v>
       </c>
       <c r="E33" s="7">
-        <v>19.600000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="F33" s="8">
-        <v>-0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G33" s="8">
-        <v>-2.33</v>
+        <v>5.24</v>
       </c>
       <c r="H33" s="9">
-        <v>0.47</v>
-      </c>
-      <c r="I33" s="10">
-        <v>197.2</v>
+        <v>0.64</v>
+      </c>
+      <c r="I33" s="8">
+        <v>36.299999999999997</v>
       </c>
       <c r="J33" s="8">
-        <v>-52.2</v>
+        <v>31</v>
       </c>
       <c r="K33" s="9">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="L33" s="8">
-        <v>-45.9</v>
+        <v>1.75</v>
+      </c>
+      <c r="L33" s="10">
+        <v>-31</v>
       </c>
       <c r="M33" s="9">
-        <v>0.47</v>
-      </c>
-      <c r="N33" s="10">
-        <v>197.2</v>
+        <v>0.64</v>
+      </c>
+      <c r="N33" s="8">
+        <v>36.299999999999997</v>
       </c>
       <c r="O33" s="8">
-        <v>-52.2</v>
+        <v>31</v>
       </c>
       <c r="P33" s="9">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>-45.9</v>
+        <v>1.75</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>-31</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="C34" s="7">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D34" s="7">
-        <v>25.5</v>
+        <v>21.99</v>
       </c>
       <c r="E34" s="7">
-        <v>20</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="F34" s="10">
-        <v>0.12</v>
+        <v>-0.5</v>
       </c>
       <c r="G34" s="10">
-        <v>0.56000000000000005</v>
+        <v>-2.33</v>
       </c>
       <c r="H34" s="9">
-        <v>0.158</v>
+        <v>0.47</v>
       </c>
       <c r="I34" s="8">
-        <v>-66.900000000000006</v>
-      </c>
-      <c r="J34" s="8">
-        <v>-53.5</v>
+        <v>197.2</v>
+      </c>
+      <c r="J34" s="10">
+        <v>-52.2</v>
       </c>
       <c r="K34" s="9">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="L34" s="8">
-        <v>-40</v>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="L34" s="10">
+        <v>-45.9</v>
       </c>
       <c r="M34" s="9">
-        <v>0.158</v>
+        <v>0.47</v>
       </c>
       <c r="N34" s="8">
-        <v>-66.900000000000006</v>
-      </c>
-      <c r="O34" s="8">
-        <v>-53.5</v>
+        <v>197.2</v>
+      </c>
+      <c r="O34" s="10">
+        <v>-52.2</v>
       </c>
       <c r="P34" s="9">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="Q34" s="8">
-        <v>-40</v>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="Q34" s="10">
+        <v>-45.9</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>3.9</v>
+        <v>21.38</v>
       </c>
       <c r="C35" s="7">
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="D35" s="7">
-        <v>21.39</v>
+        <v>25.5</v>
       </c>
       <c r="E35" s="7">
-        <v>15.7</v>
-      </c>
-      <c r="F35" s="10">
-        <v>17.48</v>
-      </c>
-      <c r="G35" s="10">
-        <v>448.21</v>
+        <v>20</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0.56000000000000005</v>
       </c>
       <c r="H35" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="I35" s="8">
-        <v>-7.2</v>
-      </c>
-      <c r="J35" s="8">
-        <v>-33.6</v>
+        <v>0.158</v>
+      </c>
+      <c r="I35" s="10">
+        <v>-66.900000000000006</v>
+      </c>
+      <c r="J35" s="10">
+        <v>-53.5</v>
       </c>
       <c r="K35" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="L35" s="8">
-        <v>-33.6</v>
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="L35" s="10">
+        <v>-40</v>
       </c>
       <c r="M35" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="N35" s="8">
-        <v>-7.2</v>
-      </c>
-      <c r="O35" s="8">
-        <v>-33.6</v>
+        <v>0.158</v>
+      </c>
+      <c r="N35" s="10">
+        <v>-66.900000000000006</v>
+      </c>
+      <c r="O35" s="10">
+        <v>-53.5</v>
       </c>
       <c r="P35" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="Q35" s="8">
-        <v>-33.6</v>
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>-40</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>17</v>
+        <v>43831</v>
+      </c>
+      <c r="B36" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="C36" s="7">
+        <v>21.38</v>
+      </c>
+      <c r="D36" s="7">
+        <v>21.39</v>
+      </c>
+      <c r="E36" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="F36" s="8">
+        <v>17.48</v>
+      </c>
+      <c r="G36" s="8">
+        <v>448.21</v>
       </c>
       <c r="H36" s="9">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="I36" s="8">
-        <v>-15.4</v>
-      </c>
-      <c r="J36" s="8">
-        <v>-51</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="I36" s="10">
+        <v>-7.2</v>
+      </c>
+      <c r="J36" s="10">
+        <v>-33.6</v>
       </c>
       <c r="K36" s="9">
-        <v>7.33</v>
-      </c>
-      <c r="L36" s="8">
-        <v>-38.6</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="L36" s="10">
+        <v>-33.6</v>
       </c>
       <c r="M36" s="9">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="N36" s="8">
-        <v>-15.4</v>
-      </c>
-      <c r="O36" s="8">
-        <v>-51</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="N36" s="10">
+        <v>-7.2</v>
+      </c>
+      <c r="O36" s="10">
+        <v>-33.6</v>
       </c>
       <c r="P36" s="9">
-        <v>7.33</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>-38.6</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>-33.6</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3097,39 +3105,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="9">
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="I37" s="8">
-        <v>-4.33</v>
-      </c>
-      <c r="J37" s="8">
-        <v>-28.7</v>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="I37" s="10">
+        <v>-15.4</v>
+      </c>
+      <c r="J37" s="10">
+        <v>-51</v>
       </c>
       <c r="K37" s="9">
-        <v>6.81</v>
-      </c>
-      <c r="L37" s="8">
-        <v>-37.4</v>
+        <v>7.33</v>
+      </c>
+      <c r="L37" s="10">
+        <v>-38.6</v>
       </c>
       <c r="M37" s="9">
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="N37" s="8">
-        <v>-4.33</v>
-      </c>
-      <c r="O37" s="8">
-        <v>-28.7</v>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="N37" s="10">
+        <v>-15.4</v>
+      </c>
+      <c r="O37" s="10">
+        <v>-51</v>
       </c>
       <c r="P37" s="9">
-        <v>6.81</v>
-      </c>
-      <c r="Q37" s="8">
-        <v>-37.4</v>
+        <v>7.33</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>-38.6</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3150,39 +3158,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="9">
-        <v>0.63700000000000001</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="I38" s="10">
-        <v>8.56</v>
-      </c>
-      <c r="J38" s="8">
-        <v>-34</v>
+        <v>-4.33</v>
+      </c>
+      <c r="J38" s="10">
+        <v>-28.7</v>
       </c>
       <c r="K38" s="9">
-        <v>6.21</v>
-      </c>
-      <c r="L38" s="8">
-        <v>-38.1</v>
+        <v>6.81</v>
+      </c>
+      <c r="L38" s="10">
+        <v>-37.4</v>
       </c>
       <c r="M38" s="9">
-        <v>0.63700000000000001</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="N38" s="10">
-        <v>8.56</v>
-      </c>
-      <c r="O38" s="8">
-        <v>-34</v>
+        <v>-4.33</v>
+      </c>
+      <c r="O38" s="10">
+        <v>-28.7</v>
       </c>
       <c r="P38" s="9">
-        <v>6.21</v>
-      </c>
-      <c r="Q38" s="8">
-        <v>-38.1</v>
+        <v>6.81</v>
+      </c>
+      <c r="Q38" s="10">
+        <v>-37.4</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3203,39 +3211,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="9">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="I39" s="10">
-        <v>50.1</v>
-      </c>
-      <c r="J39" s="8">
-        <v>-38.6</v>
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="I39" s="8">
+        <v>8.56</v>
+      </c>
+      <c r="J39" s="10">
+        <v>-34</v>
       </c>
       <c r="K39" s="9">
-        <v>5.57</v>
-      </c>
-      <c r="L39" s="8">
-        <v>-38.5</v>
+        <v>6.21</v>
+      </c>
+      <c r="L39" s="10">
+        <v>-38.1</v>
       </c>
       <c r="M39" s="9">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="N39" s="10">
-        <v>50.1</v>
-      </c>
-      <c r="O39" s="8">
-        <v>-38.6</v>
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="N39" s="8">
+        <v>8.56</v>
+      </c>
+      <c r="O39" s="10">
+        <v>-34</v>
       </c>
       <c r="P39" s="9">
-        <v>5.57</v>
-      </c>
-      <c r="Q39" s="8">
-        <v>-38.5</v>
+        <v>6.21</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>-38.1</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3256,39 +3264,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="9">
-        <v>0.39100000000000001</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="I40" s="8">
-        <v>-36.9</v>
-      </c>
-      <c r="J40" s="8">
-        <v>-62</v>
+        <v>50.1</v>
+      </c>
+      <c r="J40" s="10">
+        <v>-38.6</v>
       </c>
       <c r="K40" s="9">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="L40" s="8">
+        <v>5.57</v>
+      </c>
+      <c r="L40" s="10">
         <v>-38.5</v>
       </c>
       <c r="M40" s="9">
-        <v>0.39100000000000001</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="N40" s="8">
-        <v>-36.9</v>
-      </c>
-      <c r="O40" s="8">
-        <v>-62</v>
+        <v>50.1</v>
+      </c>
+      <c r="O40" s="10">
+        <v>-38.6</v>
       </c>
       <c r="P40" s="9">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="Q40" s="8">
+        <v>5.57</v>
+      </c>
+      <c r="Q40" s="10">
         <v>-38.5</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3309,39 +3317,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="9">
-        <v>0.62</v>
-      </c>
-      <c r="I41" s="8">
-        <v>-13.2</v>
-      </c>
-      <c r="J41" s="8">
-        <v>-48.9</v>
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="I41" s="10">
+        <v>-36.9</v>
+      </c>
+      <c r="J41" s="10">
+        <v>-62</v>
       </c>
       <c r="K41" s="9">
-        <v>4.59</v>
-      </c>
-      <c r="L41" s="8">
-        <v>-35.1</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="L41" s="10">
+        <v>-38.5</v>
       </c>
       <c r="M41" s="9">
-        <v>0.62</v>
-      </c>
-      <c r="N41" s="8">
-        <v>-13.2</v>
-      </c>
-      <c r="O41" s="8">
-        <v>-48.9</v>
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="N41" s="10">
+        <v>-36.9</v>
+      </c>
+      <c r="O41" s="10">
+        <v>-62</v>
       </c>
       <c r="P41" s="9">
-        <v>4.59</v>
-      </c>
-      <c r="Q41" s="8">
-        <v>-35.1</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>-38.5</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3362,39 +3370,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="9">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="I42" s="8">
-        <v>-1.69</v>
-      </c>
-      <c r="J42" s="8">
-        <v>-30.1</v>
+        <v>0.62</v>
+      </c>
+      <c r="I42" s="10">
+        <v>-13.2</v>
+      </c>
+      <c r="J42" s="10">
+        <v>-48.9</v>
       </c>
       <c r="K42" s="9">
-        <v>3.97</v>
-      </c>
-      <c r="L42" s="8">
-        <v>-32.299999999999997</v>
+        <v>4.59</v>
+      </c>
+      <c r="L42" s="10">
+        <v>-35.1</v>
       </c>
       <c r="M42" s="9">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="N42" s="8">
-        <v>-1.69</v>
-      </c>
-      <c r="O42" s="8">
-        <v>-30.1</v>
+        <v>0.62</v>
+      </c>
+      <c r="N42" s="10">
+        <v>-13.2</v>
+      </c>
+      <c r="O42" s="10">
+        <v>-48.9</v>
       </c>
       <c r="P42" s="9">
-        <v>3.97</v>
-      </c>
-      <c r="Q42" s="8">
-        <v>-32.299999999999997</v>
+        <v>4.59</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>-35.1</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3415,39 +3423,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="9">
-        <v>0.72599999999999998</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="I43" s="10">
-        <v>48.6</v>
-      </c>
-      <c r="J43" s="8">
-        <v>-23.4</v>
+        <v>-1.69</v>
+      </c>
+      <c r="J43" s="10">
+        <v>-30.1</v>
       </c>
       <c r="K43" s="9">
-        <v>3.26</v>
-      </c>
-      <c r="L43" s="8">
-        <v>-32.700000000000003</v>
+        <v>3.97</v>
+      </c>
+      <c r="L43" s="10">
+        <v>-32.299999999999997</v>
       </c>
       <c r="M43" s="9">
-        <v>0.72599999999999998</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="N43" s="10">
-        <v>48.6</v>
-      </c>
-      <c r="O43" s="8">
-        <v>-23.4</v>
+        <v>-1.69</v>
+      </c>
+      <c r="O43" s="10">
+        <v>-30.1</v>
       </c>
       <c r="P43" s="9">
-        <v>3.26</v>
-      </c>
-      <c r="Q43" s="8">
-        <v>-32.700000000000003</v>
+        <v>3.97</v>
+      </c>
+      <c r="Q43" s="10">
+        <v>-32.299999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3468,39 +3476,39 @@
         <v>17</v>
       </c>
       <c r="H44" s="9">
-        <v>0.48899999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="I44" s="8">
-        <v>-50.3</v>
-      </c>
-      <c r="J44" s="8">
-        <v>-58.2</v>
+        <v>48.6</v>
+      </c>
+      <c r="J44" s="10">
+        <v>-23.4</v>
       </c>
       <c r="K44" s="9">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="L44" s="8">
-        <v>-35</v>
+        <v>3.26</v>
+      </c>
+      <c r="L44" s="10">
+        <v>-32.700000000000003</v>
       </c>
       <c r="M44" s="9">
-        <v>0.48899999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="N44" s="8">
-        <v>-50.3</v>
-      </c>
-      <c r="O44" s="8">
-        <v>-58.2</v>
+        <v>48.6</v>
+      </c>
+      <c r="O44" s="10">
+        <v>-23.4</v>
       </c>
       <c r="P44" s="9">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="Q44" s="8">
-        <v>-35</v>
+        <v>3.26</v>
+      </c>
+      <c r="Q44" s="10">
+        <v>-32.700000000000003</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3521,39 +3529,39 @@
         <v>17</v>
       </c>
       <c r="H45" s="9">
-        <v>0.98399999999999999</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="I45" s="10">
-        <v>189.5</v>
-      </c>
-      <c r="J45" s="8">
-        <v>-9.39</v>
+        <v>-50.3</v>
+      </c>
+      <c r="J45" s="10">
+        <v>-58.2</v>
       </c>
       <c r="K45" s="9">
-        <v>2.04</v>
-      </c>
-      <c r="L45" s="8">
-        <v>-25</v>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="L45" s="10">
+        <v>-35</v>
       </c>
       <c r="M45" s="9">
-        <v>0.98399999999999999</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="N45" s="10">
-        <v>189.5</v>
-      </c>
-      <c r="O45" s="8">
-        <v>-9.39</v>
+        <v>-50.3</v>
+      </c>
+      <c r="O45" s="10">
+        <v>-58.2</v>
       </c>
       <c r="P45" s="9">
-        <v>2.04</v>
-      </c>
-      <c r="Q45" s="8">
-        <v>-25</v>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="Q45" s="10">
+        <v>-35</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3574,39 +3582,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="9">
-        <v>0.34</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="I46" s="8">
-        <v>-52.8</v>
-      </c>
-      <c r="J46" s="8">
-        <v>-25.1</v>
+        <v>189.5</v>
+      </c>
+      <c r="J46" s="10">
+        <v>-9.39</v>
       </c>
       <c r="K46" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="L46" s="8">
-        <v>-35.4</v>
+        <v>2.04</v>
+      </c>
+      <c r="L46" s="10">
+        <v>-25</v>
       </c>
       <c r="M46" s="9">
-        <v>0.34</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="N46" s="8">
-        <v>-52.8</v>
-      </c>
-      <c r="O46" s="8">
-        <v>-25.1</v>
+        <v>189.5</v>
+      </c>
+      <c r="O46" s="10">
+        <v>-9.39</v>
       </c>
       <c r="P46" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="Q46" s="8">
-        <v>-35.4</v>
+        <v>2.04</v>
+      </c>
+      <c r="Q46" s="10">
+        <v>-25</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3627,39 +3635,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="9">
-        <v>0.72</v>
-      </c>
-      <c r="I47" s="8">
-        <v>-31.6</v>
-      </c>
-      <c r="J47" s="8">
-        <v>-39.4</v>
+        <v>0.34</v>
+      </c>
+      <c r="I47" s="10">
+        <v>-52.8</v>
+      </c>
+      <c r="J47" s="10">
+        <v>-25.1</v>
       </c>
       <c r="K47" s="9">
-        <v>0.72</v>
-      </c>
-      <c r="L47" s="8">
-        <v>-39.4</v>
+        <v>1.06</v>
+      </c>
+      <c r="L47" s="10">
+        <v>-35.4</v>
       </c>
       <c r="M47" s="9">
-        <v>0.72</v>
-      </c>
-      <c r="N47" s="8">
-        <v>-31.6</v>
-      </c>
-      <c r="O47" s="8">
-        <v>-39.4</v>
+        <v>0.34</v>
+      </c>
+      <c r="N47" s="10">
+        <v>-52.8</v>
+      </c>
+      <c r="O47" s="10">
+        <v>-25.1</v>
       </c>
       <c r="P47" s="9">
-        <v>0.72</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>-39.4</v>
+        <v>1.06</v>
+      </c>
+      <c r="Q47" s="10">
+        <v>-35.4</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3680,39 +3688,39 @@
         <v>17</v>
       </c>
       <c r="H48" s="9">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="I48" s="10">
-        <v>23.2</v>
+        <v>-31.6</v>
       </c>
       <c r="J48" s="10">
-        <v>5.95</v>
+        <v>-39.4</v>
       </c>
       <c r="K48" s="9">
-        <v>11.93</v>
+        <v>0.72</v>
       </c>
       <c r="L48" s="10">
-        <v>6.1</v>
+        <v>-39.4</v>
       </c>
       <c r="M48" s="9">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="N48" s="10">
-        <v>23.2</v>
+        <v>-31.6</v>
       </c>
       <c r="O48" s="10">
-        <v>5.95</v>
+        <v>-39.4</v>
       </c>
       <c r="P48" s="9">
-        <v>11.93</v>
+        <v>0.72</v>
       </c>
       <c r="Q48" s="10">
-        <v>6.1</v>
+        <v>-39.4</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3733,39 +3741,39 @@
         <v>17</v>
       </c>
       <c r="H49" s="9">
-        <v>0.85399999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="I49" s="8">
-        <v>-11.4</v>
+        <v>23.2</v>
       </c>
       <c r="J49" s="8">
-        <v>-5.09</v>
+        <v>5.95</v>
       </c>
       <c r="K49" s="9">
-        <v>10.88</v>
-      </c>
-      <c r="L49" s="10">
-        <v>6.11</v>
+        <v>11.93</v>
+      </c>
+      <c r="L49" s="8">
+        <v>6.1</v>
       </c>
       <c r="M49" s="9">
-        <v>0.85399999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="N49" s="8">
-        <v>-11.4</v>
+        <v>23.2</v>
       </c>
       <c r="O49" s="8">
-        <v>-5.09</v>
+        <v>5.95</v>
       </c>
       <c r="P49" s="9">
-        <v>10.88</v>
-      </c>
-      <c r="Q49" s="10">
-        <v>6.11</v>
+        <v>11.93</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>6.1</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3786,39 +3794,39 @@
         <v>17</v>
       </c>
       <c r="H50" s="9">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>17</v>
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="I50" s="10">
+        <v>-11.4</v>
       </c>
       <c r="J50" s="10">
-        <v>12.4</v>
+        <v>-5.09</v>
       </c>
       <c r="K50" s="9">
-        <v>10.02</v>
-      </c>
-      <c r="L50" s="10">
-        <v>7.19</v>
+        <v>10.88</v>
+      </c>
+      <c r="L50" s="8">
+        <v>6.11</v>
       </c>
       <c r="M50" s="9">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="N50" s="9" t="s">
-        <v>17</v>
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="N50" s="10">
+        <v>-11.4</v>
       </c>
       <c r="O50" s="10">
-        <v>12.4</v>
+        <v>-5.09</v>
       </c>
       <c r="P50" s="9">
-        <v>10.02</v>
-      </c>
-      <c r="Q50" s="10">
-        <v>7.19</v>
+        <v>10.88</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>6.11</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>40756</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3839,39 +3847,39 @@
         <v>17</v>
       </c>
       <c r="H51" s="9">
-        <v>0.747</v>
-      </c>
-      <c r="I51" s="10">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="8">
         <v>12.4</v>
       </c>
-      <c r="J51" s="10">
-        <v>53.2</v>
-      </c>
       <c r="K51" s="9">
-        <v>5.12</v>
-      </c>
-      <c r="L51" s="10">
-        <v>55.1</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>17</v>
+        <v>10.02</v>
+      </c>
+      <c r="L51" s="8">
+        <v>7.19</v>
+      </c>
+      <c r="M51" s="9">
+        <v>0.96399999999999997</v>
       </c>
       <c r="N51" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q51" s="9" t="s">
-        <v>17</v>
+      <c r="O51" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="P51" s="9">
+        <v>10.02</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>7.19</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>40725</v>
+        <v>40756</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3892,19 +3900,19 @@
         <v>17</v>
       </c>
       <c r="H52" s="9">
-        <v>0.66500000000000004</v>
+        <v>0.747</v>
       </c>
       <c r="I52" s="8">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="J52" s="10">
-        <v>24.6</v>
+        <v>12.4</v>
+      </c>
+      <c r="J52" s="8">
+        <v>53.2</v>
       </c>
       <c r="K52" s="9">
-        <v>4.38</v>
-      </c>
-      <c r="L52" s="10">
-        <v>55.5</v>
+        <v>5.12</v>
+      </c>
+      <c r="L52" s="8">
+        <v>55.1</v>
       </c>
       <c r="M52" s="9" t="s">
         <v>17</v>
@@ -3924,7 +3932,7 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>40695</v>
+        <v>40725</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3945,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="H53" s="9">
-        <v>0.83</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="I53" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="J53" s="10">
-        <v>164.9</v>
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="J53" s="8">
+        <v>24.6</v>
       </c>
       <c r="K53" s="9">
-        <v>3.71</v>
-      </c>
-      <c r="L53" s="10">
-        <v>62.7</v>
+        <v>4.38</v>
+      </c>
+      <c r="L53" s="8">
+        <v>55.5</v>
       </c>
       <c r="M53" s="9" t="s">
         <v>17</v>
@@ -3977,7 +3985,7 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>40664</v>
+        <v>40695</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4000,17 +4008,17 @@
       <c r="H54" s="9">
         <v>0.83</v>
       </c>
-      <c r="I54" s="10">
-        <v>71.2</v>
-      </c>
-      <c r="J54" s="10">
-        <v>85</v>
+      <c r="I54" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="J54" s="8">
+        <v>164.9</v>
       </c>
       <c r="K54" s="9">
-        <v>2.88</v>
-      </c>
-      <c r="L54" s="10">
-        <v>46.4</v>
+        <v>3.71</v>
+      </c>
+      <c r="L54" s="8">
+        <v>62.7</v>
       </c>
       <c r="M54" s="9" t="s">
         <v>17</v>
@@ -4030,7 +4038,7 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>40634</v>
+        <v>40664</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4051,19 +4059,19 @@
         <v>17</v>
       </c>
       <c r="H55" s="9">
-        <v>0.48499999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="I55" s="8">
-        <v>-23.9</v>
-      </c>
-      <c r="J55" s="10">
-        <v>40.799999999999997</v>
+        <v>71.2</v>
+      </c>
+      <c r="J55" s="8">
+        <v>85</v>
       </c>
       <c r="K55" s="9">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="L55" s="10">
-        <v>35</v>
+        <v>2.88</v>
+      </c>
+      <c r="L55" s="8">
+        <v>46.4</v>
       </c>
       <c r="M55" s="9" t="s">
         <v>17</v>
@@ -4083,7 +4091,7 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>40603</v>
+        <v>40634</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4104,19 +4112,19 @@
         <v>17</v>
       </c>
       <c r="H56" s="9">
-        <v>0.63700000000000001</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="I56" s="10">
-        <v>58.4</v>
-      </c>
-      <c r="J56" s="10">
-        <v>48.6</v>
+        <v>-23.9</v>
+      </c>
+      <c r="J56" s="8">
+        <v>40.799999999999997</v>
       </c>
       <c r="K56" s="9">
-        <v>1.57</v>
-      </c>
-      <c r="L56" s="10">
-        <v>33.4</v>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L56" s="8">
+        <v>35</v>
       </c>
       <c r="M56" s="9" t="s">
         <v>17</v>
@@ -4136,7 +4144,7 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>40575</v>
+        <v>40603</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4157,19 +4165,19 @@
         <v>17</v>
       </c>
       <c r="H57" s="9">
-        <v>0.40200000000000002</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="I57" s="8">
-        <v>-23.8</v>
-      </c>
-      <c r="J57" s="10">
-        <v>67.3</v>
+        <v>58.4</v>
+      </c>
+      <c r="J57" s="8">
+        <v>48.6</v>
       </c>
       <c r="K57" s="9">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="L57" s="10">
-        <v>24.6</v>
+        <v>1.57</v>
+      </c>
+      <c r="L57" s="8">
+        <v>33.4</v>
       </c>
       <c r="M57" s="9" t="s">
         <v>17</v>
@@ -4189,7 +4197,7 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>40544</v>
+        <v>40575</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4210,19 +4218,19 @@
         <v>17</v>
       </c>
       <c r="H58" s="9">
-        <v>0.52700000000000002</v>
-      </c>
-      <c r="I58" s="8">
-        <v>-3.51</v>
-      </c>
-      <c r="J58" s="10">
-        <v>4.3600000000000003</v>
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="I58" s="10">
+        <v>-23.8</v>
+      </c>
+      <c r="J58" s="8">
+        <v>67.3</v>
       </c>
       <c r="K58" s="9">
-        <v>0.52700000000000002</v>
-      </c>
-      <c r="L58" s="10">
-        <v>4.3600000000000003</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="L58" s="8">
+        <v>24.6</v>
       </c>
       <c r="M58" s="9" t="s">
         <v>17</v>
@@ -4242,7 +4250,7 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>40513</v>
+        <v>40544</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4263,19 +4271,19 @@
         <v>17</v>
       </c>
       <c r="H59" s="9">
-        <v>0.54700000000000004</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="I59" s="10">
-        <v>11</v>
-      </c>
-      <c r="J59" s="10">
-        <v>182.1</v>
+        <v>-3.51</v>
+      </c>
+      <c r="J59" s="8">
+        <v>4.3600000000000003</v>
       </c>
       <c r="K59" s="9">
-        <v>5.78</v>
-      </c>
-      <c r="L59" s="10">
-        <v>83.1</v>
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="L59" s="8">
+        <v>4.3600000000000003</v>
       </c>
       <c r="M59" s="9" t="s">
         <v>17</v>
@@ -4295,7 +4303,7 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>40483</v>
+        <v>40513</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4316,19 +4324,19 @@
         <v>17</v>
       </c>
       <c r="H60" s="9">
-        <v>0.49199999999999999</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="I60" s="8">
-        <v>-17.600000000000001</v>
-      </c>
-      <c r="J60" s="10">
-        <v>129.4</v>
+        <v>11</v>
+      </c>
+      <c r="J60" s="8">
+        <v>182.1</v>
       </c>
       <c r="K60" s="9">
-        <v>5.23</v>
-      </c>
-      <c r="L60" s="10">
-        <v>76.599999999999994</v>
+        <v>5.78</v>
+      </c>
+      <c r="L60" s="8">
+        <v>83.1</v>
       </c>
       <c r="M60" s="9" t="s">
         <v>17</v>
@@ -4348,7 +4356,7 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>40452</v>
+        <v>40483</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4369,19 +4377,19 @@
         <v>17</v>
       </c>
       <c r="H61" s="9">
-        <v>0.59799999999999998</v>
-      </c>
-      <c r="I61" s="8">
-        <v>-29</v>
-      </c>
-      <c r="J61" s="10">
-        <v>121.1</v>
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="I61" s="10">
+        <v>-17.600000000000001</v>
+      </c>
+      <c r="J61" s="8">
+        <v>129.4</v>
       </c>
       <c r="K61" s="9">
-        <v>4.74</v>
-      </c>
-      <c r="L61" s="10">
-        <v>72.5</v>
+        <v>5.23</v>
+      </c>
+      <c r="L61" s="8">
+        <v>76.599999999999994</v>
       </c>
       <c r="M61" s="9" t="s">
         <v>17</v>
@@ -4401,7 +4409,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>40422</v>
+        <v>40452</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4422,19 +4430,19 @@
         <v>17</v>
       </c>
       <c r="H62" s="9">
-        <v>0.84199999999999997</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="I62" s="10">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="J62" s="10">
-        <v>250.1</v>
+        <v>-29</v>
+      </c>
+      <c r="J62" s="8">
+        <v>121.1</v>
       </c>
       <c r="K62" s="9">
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="L62" s="10">
-        <v>67.2</v>
+        <v>4.74</v>
+      </c>
+      <c r="L62" s="8">
+        <v>72.5</v>
       </c>
       <c r="M62" s="9" t="s">
         <v>17</v>
@@ -4454,7 +4462,7 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>40391</v>
+        <v>40422</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4475,19 +4483,19 @@
         <v>17</v>
       </c>
       <c r="H63" s="9">
-        <v>0.48799999999999999</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="I63" s="8">
-        <v>-8.59</v>
-      </c>
-      <c r="J63" s="10">
-        <v>54.4</v>
+        <v>72.599999999999994</v>
+      </c>
+      <c r="J63" s="8">
+        <v>250.1</v>
       </c>
       <c r="K63" s="9">
-        <v>3.3</v>
-      </c>
-      <c r="L63" s="10">
-        <v>47.5</v>
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L63" s="8">
+        <v>67.2</v>
       </c>
       <c r="M63" s="9" t="s">
         <v>17</v>
@@ -4507,7 +4515,7 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>40360</v>
+        <v>40391</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4528,19 +4536,19 @@
         <v>17</v>
       </c>
       <c r="H64" s="9">
-        <v>0.53400000000000003</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="I64" s="10">
-        <v>70.2</v>
-      </c>
-      <c r="J64" s="10">
-        <v>85.3</v>
+        <v>-8.59</v>
+      </c>
+      <c r="J64" s="8">
+        <v>54.4</v>
       </c>
       <c r="K64" s="9">
-        <v>2.81</v>
-      </c>
-      <c r="L64" s="10">
-        <v>46.4</v>
+        <v>3.3</v>
+      </c>
+      <c r="L64" s="8">
+        <v>47.5</v>
       </c>
       <c r="M64" s="9" t="s">
         <v>17</v>
@@ -4560,7 +4568,7 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>40330</v>
+        <v>40360</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4581,19 +4589,19 @@
         <v>17</v>
       </c>
       <c r="H65" s="9">
-        <v>0.313</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="I65" s="8">
-        <v>-30.1</v>
-      </c>
-      <c r="J65" s="10">
-        <v>23.8</v>
+        <v>70.2</v>
+      </c>
+      <c r="J65" s="8">
+        <v>85.3</v>
       </c>
       <c r="K65" s="9">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="L65" s="10">
-        <v>39.5</v>
+        <v>2.81</v>
+      </c>
+      <c r="L65" s="8">
+        <v>46.4</v>
       </c>
       <c r="M65" s="9" t="s">
         <v>17</v>
@@ -4613,7 +4621,7 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>40299</v>
+        <v>40330</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4634,19 +4642,19 @@
         <v>17</v>
       </c>
       <c r="H66" s="9">
-        <v>0.44900000000000001</v>
+        <v>0.313</v>
       </c>
       <c r="I66" s="10">
-        <v>30.3</v>
-      </c>
-      <c r="J66" s="10">
-        <v>121.5</v>
+        <v>-30.1</v>
+      </c>
+      <c r="J66" s="8">
+        <v>23.8</v>
       </c>
       <c r="K66" s="9">
-        <v>1.97</v>
-      </c>
-      <c r="L66" s="10">
-        <v>42.4</v>
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="L66" s="8">
+        <v>39.5</v>
       </c>
       <c r="M66" s="9" t="s">
         <v>17</v>
@@ -4666,7 +4674,7 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>40269</v>
+        <v>40299</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4687,19 +4695,19 @@
         <v>17</v>
       </c>
       <c r="H67" s="9">
-        <v>0.34399999999999997</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="I67" s="8">
-        <v>-19.600000000000001</v>
-      </c>
-      <c r="J67" s="10">
-        <v>23.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="J67" s="8">
+        <v>121.5</v>
       </c>
       <c r="K67" s="9">
-        <v>1.52</v>
-      </c>
-      <c r="L67" s="10">
-        <v>28.8</v>
+        <v>1.97</v>
+      </c>
+      <c r="L67" s="8">
+        <v>42.4</v>
       </c>
       <c r="M67" s="9" t="s">
         <v>17</v>
@@ -4719,7 +4727,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>40238</v>
+        <v>40269</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4740,19 +4748,19 @@
         <v>17</v>
       </c>
       <c r="H68" s="9">
-        <v>0.42899999999999999</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="I68" s="10">
-        <v>78.3</v>
-      </c>
-      <c r="J68" s="10">
-        <v>101.7</v>
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="J68" s="8">
+        <v>23.9</v>
       </c>
       <c r="K68" s="9">
-        <v>1.17</v>
-      </c>
-      <c r="L68" s="10">
-        <v>30.3</v>
+        <v>1.52</v>
+      </c>
+      <c r="L68" s="8">
+        <v>28.8</v>
       </c>
       <c r="M68" s="9" t="s">
         <v>17</v>
@@ -4772,7 +4780,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>40210</v>
+        <v>40238</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4793,19 +4801,19 @@
         <v>17</v>
       </c>
       <c r="H69" s="9">
-        <v>0.24</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="I69" s="8">
-        <v>-52.4</v>
+        <v>78.3</v>
       </c>
       <c r="J69" s="8">
-        <v>-46.3</v>
+        <v>101.7</v>
       </c>
       <c r="K69" s="9">
-        <v>0.746</v>
-      </c>
-      <c r="L69" s="10">
-        <v>8.26</v>
+        <v>1.17</v>
+      </c>
+      <c r="L69" s="8">
+        <v>30.3</v>
       </c>
       <c r="M69" s="9" t="s">
         <v>17</v>
@@ -4825,7 +4833,7 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>40179</v>
+        <v>40210</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4846,19 +4854,19 @@
         <v>17</v>
       </c>
       <c r="H70" s="9">
-        <v>0.505</v>
+        <v>0.24</v>
       </c>
       <c r="I70" s="10">
-        <v>160.80000000000001</v>
+        <v>-52.4</v>
       </c>
       <c r="J70" s="10">
-        <v>109.4</v>
+        <v>-46.3</v>
       </c>
       <c r="K70" s="9">
-        <v>0.505</v>
-      </c>
-      <c r="L70" s="10">
-        <v>109.4</v>
+        <v>0.746</v>
+      </c>
+      <c r="L70" s="8">
+        <v>8.26</v>
       </c>
       <c r="M70" s="9" t="s">
         <v>17</v>
@@ -4878,7 +4886,7 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>40148</v>
+        <v>40179</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4899,31 +4907,31 @@
         <v>17</v>
       </c>
       <c r="H71" s="9">
-        <v>0.19400000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="I71" s="8">
-        <v>-9.75</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="J71" s="8">
-        <v>-70.8</v>
+        <v>109.4</v>
       </c>
       <c r="K71" s="9">
-        <v>3.16</v>
+        <v>0.505</v>
       </c>
       <c r="L71" s="8">
-        <v>-62.5</v>
-      </c>
-      <c r="M71" s="9">
-        <v>1.79</v>
-      </c>
-      <c r="N71" s="10">
-        <v>12.1</v>
+        <v>109.4</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P71" s="9">
-        <v>16.89</v>
+      <c r="P71" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="Q71" s="9" t="s">
         <v>17</v>
@@ -4931,7 +4939,7 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>40118</v>
+        <v>40148</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4952,31 +4960,31 @@
         <v>17</v>
       </c>
       <c r="H72" s="9">
-        <v>0.215</v>
-      </c>
-      <c r="I72" s="8">
-        <v>-20.6</v>
-      </c>
-      <c r="J72" s="8">
-        <v>-69.900000000000006</v>
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="I72" s="10">
+        <v>-9.75</v>
+      </c>
+      <c r="J72" s="10">
+        <v>-70.8</v>
       </c>
       <c r="K72" s="9">
-        <v>2.96</v>
-      </c>
-      <c r="L72" s="8">
-        <v>-61.8</v>
+        <v>3.16</v>
+      </c>
+      <c r="L72" s="10">
+        <v>-62.5</v>
       </c>
       <c r="M72" s="9">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="N72" s="8">
-        <v>-6.6</v>
+        <v>12.1</v>
       </c>
       <c r="O72" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P72" s="9">
-        <v>15.1</v>
+        <v>16.89</v>
       </c>
       <c r="Q72" s="9" t="s">
         <v>17</v>
@@ -4984,7 +4992,7 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>40087</v>
+        <v>40118</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5005,31 +5013,31 @@
         <v>17</v>
       </c>
       <c r="H73" s="9">
-        <v>0.27</v>
+        <v>0.215</v>
       </c>
       <c r="I73" s="10">
-        <v>12.5</v>
-      </c>
-      <c r="J73" s="8">
-        <v>-57.7</v>
+        <v>-20.6</v>
+      </c>
+      <c r="J73" s="10">
+        <v>-69.900000000000006</v>
       </c>
       <c r="K73" s="9">
-        <v>2.75</v>
-      </c>
-      <c r="L73" s="8">
-        <v>-61</v>
+        <v>2.96</v>
+      </c>
+      <c r="L73" s="10">
+        <v>-61.8</v>
       </c>
       <c r="M73" s="9">
-        <v>1.71</v>
-      </c>
-      <c r="N73" s="8">
-        <v>-1.41</v>
+        <v>1.59</v>
+      </c>
+      <c r="N73" s="10">
+        <v>-6.6</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P73" s="9">
-        <v>13.51</v>
+        <v>15.1</v>
       </c>
       <c r="Q73" s="9" t="s">
         <v>17</v>
@@ -5037,52 +5045,52 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>40057</v>
-      </c>
-      <c r="B74" s="7">
-        <v>4</v>
-      </c>
-      <c r="C74" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="D74" s="7">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="E74" s="7">
-        <v>3.85</v>
-      </c>
-      <c r="F74" s="8">
-        <v>-0.1</v>
-      </c>
-      <c r="G74" s="8">
-        <v>-2.5</v>
+        <v>40087</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="H74" s="9">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="I74" s="8">
-        <v>-23.9</v>
-      </c>
-      <c r="J74" s="8">
-        <v>-73</v>
+        <v>12.5</v>
+      </c>
+      <c r="J74" s="10">
+        <v>-57.7</v>
       </c>
       <c r="K74" s="9">
-        <v>2.48</v>
-      </c>
-      <c r="L74" s="8">
-        <v>-61.3</v>
+        <v>2.75</v>
+      </c>
+      <c r="L74" s="10">
+        <v>-61</v>
       </c>
       <c r="M74" s="9">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="N74" s="10">
-        <v>11.2</v>
+        <v>-1.41</v>
       </c>
       <c r="O74" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P74" s="9">
-        <v>11.8</v>
+        <v>13.51</v>
       </c>
       <c r="Q74" s="9" t="s">
         <v>17</v>
@@ -5090,52 +5098,52 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>40026</v>
+        <v>40057</v>
       </c>
       <c r="B75" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D75" s="7">
-        <v>6</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="E75" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="F75" s="8">
-        <v>-1</v>
-      </c>
-      <c r="G75" s="8">
-        <v>-20</v>
+        <v>3.85</v>
+      </c>
+      <c r="F75" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-2.5</v>
       </c>
       <c r="H75" s="9">
-        <v>0.316</v>
+        <v>0.24</v>
       </c>
       <c r="I75" s="10">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="J75" s="8">
-        <v>-56.7</v>
+        <v>-23.9</v>
+      </c>
+      <c r="J75" s="10">
+        <v>-73</v>
       </c>
       <c r="K75" s="9">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="L75" s="8">
-        <v>-59.5</v>
+        <v>2.48</v>
+      </c>
+      <c r="L75" s="10">
+        <v>-61.3</v>
       </c>
       <c r="M75" s="9">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="N75" s="8">
-        <v>-7.87</v>
+        <v>11.2</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P75" s="9">
-        <v>10.07</v>
+        <v>11.8</v>
       </c>
       <c r="Q75" s="9" t="s">
         <v>17</v>
@@ -5143,52 +5151,52 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>39995</v>
+        <v>40026</v>
       </c>
       <c r="B76" s="7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C76" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D76" s="7">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="E76" s="7">
-        <v>5</v>
-      </c>
-      <c r="F76" s="8">
-        <v>-1.25</v>
-      </c>
-      <c r="G76" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F76" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G76" s="10">
         <v>-20</v>
       </c>
       <c r="H76" s="9">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="I76" s="10">
-        <v>13.8</v>
-      </c>
-      <c r="J76" s="8">
-        <v>-48.9</v>
+        <v>0.316</v>
+      </c>
+      <c r="I76" s="8">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="J76" s="10">
+        <v>-56.7</v>
       </c>
       <c r="K76" s="9">
-        <v>1.92</v>
-      </c>
-      <c r="L76" s="8">
-        <v>-59.9</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="L76" s="10">
+        <v>-59.5</v>
       </c>
       <c r="M76" s="9">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="N76" s="10">
-        <v>19</v>
+        <v>-7.87</v>
       </c>
       <c r="O76" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P76" s="9">
-        <v>8.51</v>
+        <v>10.07</v>
       </c>
       <c r="Q76" s="9" t="s">
         <v>17</v>
@@ -5196,52 +5204,52 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>39965</v>
+        <v>39995</v>
       </c>
       <c r="B77" s="7">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C77" s="7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="D77" s="7">
-        <v>7.03</v>
+        <v>6.7</v>
       </c>
       <c r="E77" s="7">
-        <v>6.25</v>
-      </c>
-      <c r="F77" s="8">
-        <v>-0.75</v>
-      </c>
-      <c r="G77" s="8">
-        <v>-10.71</v>
+        <v>5</v>
+      </c>
+      <c r="F77" s="10">
+        <v>-1.25</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-20</v>
       </c>
       <c r="H77" s="9">
-        <v>0.253</v>
-      </c>
-      <c r="I77" s="10">
-        <v>24.9</v>
-      </c>
-      <c r="J77" s="8">
-        <v>-63.2</v>
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="I77" s="8">
+        <v>13.8</v>
+      </c>
+      <c r="J77" s="10">
+        <v>-48.9</v>
       </c>
       <c r="K77" s="9">
-        <v>1.63</v>
-      </c>
-      <c r="L77" s="8">
-        <v>-61.3</v>
+        <v>1.92</v>
+      </c>
+      <c r="L77" s="10">
+        <v>-59.9</v>
       </c>
       <c r="M77" s="9">
-        <v>1.42</v>
-      </c>
-      <c r="N77" s="10">
-        <v>9.19</v>
+        <v>1.69</v>
+      </c>
+      <c r="N77" s="8">
+        <v>19</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P77" s="9">
-        <v>6.82</v>
+        <v>8.51</v>
       </c>
       <c r="Q77" s="9" t="s">
         <v>17</v>
@@ -5249,52 +5257,52 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>39934</v>
+        <v>39965</v>
       </c>
       <c r="B78" s="7">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="C78" s="7">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="D78" s="7">
-        <v>7.6</v>
+        <v>7.03</v>
       </c>
       <c r="E78" s="7">
-        <v>7</v>
-      </c>
-      <c r="F78" s="8">
-        <v>-0.6</v>
-      </c>
-      <c r="G78" s="8">
-        <v>-7.89</v>
+        <v>6.25</v>
+      </c>
+      <c r="F78" s="10">
+        <v>-0.75</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-10.71</v>
       </c>
       <c r="H78" s="9">
-        <v>0.20300000000000001</v>
+        <v>0.253</v>
       </c>
       <c r="I78" s="8">
-        <v>-27.1</v>
-      </c>
-      <c r="J78" s="8">
-        <v>-77.7</v>
+        <v>24.9</v>
+      </c>
+      <c r="J78" s="10">
+        <v>-63.2</v>
       </c>
       <c r="K78" s="9">
-        <v>1.38</v>
-      </c>
-      <c r="L78" s="8">
-        <v>-61</v>
+        <v>1.63</v>
+      </c>
+      <c r="L78" s="10">
+        <v>-61.3</v>
       </c>
       <c r="M78" s="9">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="N78" s="8">
-        <v>-1.81</v>
+        <v>9.19</v>
       </c>
       <c r="O78" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P78" s="9">
-        <v>5.4</v>
+        <v>6.82</v>
       </c>
       <c r="Q78" s="9" t="s">
         <v>17</v>
@@ -5302,52 +5310,52 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>39904</v>
+        <v>39934</v>
       </c>
       <c r="B79" s="7">
-        <v>7.41</v>
+        <v>7.6</v>
       </c>
       <c r="C79" s="7">
+        <v>7</v>
+      </c>
+      <c r="D79" s="7">
         <v>7.6</v>
       </c>
-      <c r="D79" s="7">
-        <v>8.1999999999999993</v>
-      </c>
       <c r="E79" s="7">
-        <v>7.22</v>
+        <v>7</v>
       </c>
       <c r="F79" s="10">
-        <v>0.19</v>
+        <v>-0.6</v>
       </c>
       <c r="G79" s="10">
-        <v>2.56</v>
+        <v>-7.89</v>
       </c>
       <c r="H79" s="9">
-        <v>0.27800000000000002</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="I79" s="10">
-        <v>30.8</v>
-      </c>
-      <c r="J79" s="8">
-        <v>-62.7</v>
+        <v>-27.1</v>
+      </c>
+      <c r="J79" s="10">
+        <v>-77.7</v>
       </c>
       <c r="K79" s="9">
-        <v>1.18</v>
-      </c>
-      <c r="L79" s="8">
-        <v>-55.2</v>
+        <v>1.38</v>
+      </c>
+      <c r="L79" s="10">
+        <v>-61</v>
       </c>
       <c r="M79" s="9">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="N79" s="10">
-        <v>26.7</v>
+        <v>-1.81</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P79" s="9">
-        <v>4.0999999999999996</v>
+        <v>5.4</v>
       </c>
       <c r="Q79" s="9" t="s">
         <v>17</v>
@@ -5355,52 +5363,52 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>39873</v>
+        <v>39904</v>
       </c>
       <c r="B80" s="7">
-        <v>8.1999999999999993</v>
+        <v>7.41</v>
       </c>
       <c r="C80" s="7">
-        <v>7.41</v>
+        <v>7.6</v>
       </c>
       <c r="D80" s="7">
         <v>8.1999999999999993</v>
       </c>
       <c r="E80" s="7">
-        <v>7.41</v>
+        <v>7.22</v>
       </c>
       <c r="F80" s="8">
-        <v>-0.79</v>
+        <v>0.19</v>
       </c>
       <c r="G80" s="8">
-        <v>-9.6300000000000008</v>
+        <v>2.56</v>
       </c>
       <c r="H80" s="9">
-        <v>0.21199999999999999</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="I80" s="8">
-        <v>-52.5</v>
-      </c>
-      <c r="J80" s="8">
-        <v>-67.400000000000006</v>
+        <v>30.8</v>
+      </c>
+      <c r="J80" s="10">
+        <v>-62.7</v>
       </c>
       <c r="K80" s="9">
-        <v>0.90100000000000002</v>
-      </c>
-      <c r="L80" s="8">
-        <v>-52.2</v>
+        <v>1.18</v>
+      </c>
+      <c r="L80" s="10">
+        <v>-55.2</v>
       </c>
       <c r="M80" s="9">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="N80" s="8">
-        <v>-3.84</v>
+        <v>26.7</v>
       </c>
       <c r="O80" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P80" s="9">
-        <v>2.78</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Q80" s="9" t="s">
         <v>17</v>
@@ -5408,52 +5416,52 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>39845</v>
+        <v>39873</v>
       </c>
       <c r="B81" s="7">
-        <v>7.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="C81" s="7">
-        <v>8.1999999999999993</v>
+        <v>7.41</v>
       </c>
       <c r="D81" s="7">
         <v>8.1999999999999993</v>
       </c>
       <c r="E81" s="7">
-        <v>7.5</v>
+        <v>7.41</v>
       </c>
       <c r="F81" s="10">
-        <v>0.5</v>
+        <v>-0.79</v>
       </c>
       <c r="G81" s="10">
-        <v>6.49</v>
+        <v>-9.6300000000000008</v>
       </c>
       <c r="H81" s="9">
-        <v>0.44700000000000001</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="I81" s="10">
-        <v>85.4</v>
-      </c>
-      <c r="J81" s="8">
-        <v>-12</v>
+        <v>-52.5</v>
+      </c>
+      <c r="J81" s="10">
+        <v>-67.400000000000006</v>
       </c>
       <c r="K81" s="9">
-        <v>0.68899999999999995</v>
-      </c>
-      <c r="L81" s="8">
-        <v>-44.2</v>
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="L81" s="10">
+        <v>-52.2</v>
       </c>
       <c r="M81" s="9">
-        <v>1.0900000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="N81" s="10">
-        <v>67.3</v>
+        <v>-3.84</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P81" s="9">
-        <v>1.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q81" s="9" t="s">
         <v>17</v>
@@ -5461,52 +5469,52 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>39814</v>
+        <v>39845</v>
       </c>
       <c r="B82" s="7">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="C82" s="7">
-        <v>7.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="D82" s="7">
-        <v>8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E82" s="7">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F82" s="8">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G82" s="8">
-        <v>-3.75</v>
+        <v>6.49</v>
       </c>
       <c r="H82" s="9">
-        <v>0.24099999999999999</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="I82" s="8">
-        <v>-63.6</v>
-      </c>
-      <c r="J82" s="8">
-        <v>-66.8</v>
+        <v>85.4</v>
+      </c>
+      <c r="J82" s="10">
+        <v>-12</v>
       </c>
       <c r="K82" s="9">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="L82" s="8">
-        <v>-66.8</v>
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="L82" s="10">
+        <v>-44.2</v>
       </c>
       <c r="M82" s="9">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="N82" s="9" t="s">
-        <v>17</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N82" s="8">
+        <v>67.3</v>
       </c>
       <c r="O82" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P82" s="9">
-        <v>0.64900000000000002</v>
+        <v>1.74</v>
       </c>
       <c r="Q82" s="9" t="s">
         <v>17</v>
@@ -5514,43 +5522,43 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>39783</v>
+        <v>39814</v>
       </c>
       <c r="B83" s="7">
-        <v>7.05</v>
+        <v>8</v>
       </c>
       <c r="C83" s="7">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="D83" s="7">
         <v>8</v>
       </c>
       <c r="E83" s="7">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="F83" s="10">
-        <v>0.95</v>
+        <v>-0.3</v>
       </c>
       <c r="G83" s="10">
-        <v>13.48</v>
+        <v>-3.75</v>
       </c>
       <c r="H83" s="9">
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="I83" s="8">
-        <v>-6.94</v>
-      </c>
-      <c r="J83" s="8">
-        <v>-22.1</v>
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="I83" s="10">
+        <v>-63.6</v>
+      </c>
+      <c r="J83" s="10">
+        <v>-66.8</v>
       </c>
       <c r="K83" s="9">
-        <v>8.43</v>
-      </c>
-      <c r="L83" s="8">
-        <v>-5.71</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>17</v>
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="L83" s="10">
+        <v>-66.8</v>
+      </c>
+      <c r="M83" s="9">
+        <v>0.64900000000000002</v>
       </c>
       <c r="N83" s="9" t="s">
         <v>17</v>
@@ -5558,8 +5566,8 @@
       <c r="O83" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="9" t="s">
-        <v>17</v>
+      <c r="P83" s="9">
+        <v>0.64900000000000002</v>
       </c>
       <c r="Q83" s="9" t="s">
         <v>17</v>
@@ -5567,40 +5575,40 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>39753</v>
+        <v>39783</v>
       </c>
       <c r="B84" s="7">
-        <v>7.26</v>
+        <v>7.05</v>
       </c>
       <c r="C84" s="7">
-        <v>7.05</v>
+        <v>8</v>
       </c>
       <c r="D84" s="7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E84" s="7">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="F84" s="8">
-        <v>-0.21</v>
+        <v>0.95</v>
       </c>
       <c r="G84" s="8">
-        <v>-2.89</v>
+        <v>13.48</v>
       </c>
       <c r="H84" s="9">
-        <v>0.71199999999999997</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="I84" s="10">
-        <v>11.4</v>
-      </c>
-      <c r="J84" s="8">
-        <v>-3.94</v>
+        <v>-6.94</v>
+      </c>
+      <c r="J84" s="10">
+        <v>-22.1</v>
       </c>
       <c r="K84" s="9">
-        <v>7.76</v>
-      </c>
-      <c r="L84" s="8">
-        <v>-3.98</v>
+        <v>8.43</v>
+      </c>
+      <c r="L84" s="10">
+        <v>-5.71</v>
       </c>
       <c r="M84" s="9" t="s">
         <v>17</v>
@@ -5620,40 +5628,40 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>39722</v>
+        <v>39753</v>
       </c>
       <c r="B85" s="7">
-        <v>12.6</v>
+        <v>7.26</v>
       </c>
       <c r="C85" s="7">
-        <v>7.26</v>
+        <v>7.05</v>
       </c>
       <c r="D85" s="7">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="E85" s="7">
-        <v>6.9</v>
-      </c>
-      <c r="F85" s="8">
-        <v>-5.34</v>
-      </c>
-      <c r="G85" s="8">
-        <v>-42.38</v>
+        <v>6.52</v>
+      </c>
+      <c r="F85" s="10">
+        <v>-0.21</v>
+      </c>
+      <c r="G85" s="10">
+        <v>-2.89</v>
       </c>
       <c r="H85" s="9">
-        <v>0.63900000000000001</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="I85" s="8">
-        <v>-28.2</v>
-      </c>
-      <c r="J85" s="8">
-        <v>-37.799999999999997</v>
+        <v>11.4</v>
+      </c>
+      <c r="J85" s="10">
+        <v>-3.94</v>
       </c>
       <c r="K85" s="9">
-        <v>7.05</v>
-      </c>
-      <c r="L85" s="8">
-        <v>-3.99</v>
+        <v>7.76</v>
+      </c>
+      <c r="L85" s="10">
+        <v>-3.98</v>
       </c>
       <c r="M85" s="9" t="s">
         <v>17</v>
@@ -5673,40 +5681,40 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>39692</v>
+        <v>39722</v>
       </c>
       <c r="B86" s="7">
-        <v>16</v>
+        <v>12.6</v>
       </c>
       <c r="C86" s="7">
-        <v>12.6</v>
+        <v>7.26</v>
       </c>
       <c r="D86" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E86" s="7">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="F86" s="8">
-        <v>-3.4</v>
-      </c>
-      <c r="G86" s="8">
-        <v>-21.25</v>
+        <v>6.9</v>
+      </c>
+      <c r="F86" s="10">
+        <v>-5.34</v>
+      </c>
+      <c r="G86" s="10">
+        <v>-42.38</v>
       </c>
       <c r="H86" s="9">
-        <v>0.89100000000000001</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="I86" s="10">
-        <v>22</v>
+        <v>-28.2</v>
       </c>
       <c r="J86" s="10">
-        <v>54.4</v>
+        <v>-37.799999999999997</v>
       </c>
       <c r="K86" s="9">
-        <v>6.41</v>
+        <v>7.05</v>
       </c>
       <c r="L86" s="10">
-        <v>1.51</v>
+        <v>-3.99</v>
       </c>
       <c r="M86" s="9" t="s">
         <v>17</v>
@@ -5726,40 +5734,40 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>39661</v>
+        <v>39692</v>
       </c>
       <c r="B87" s="7">
-        <v>14.7</v>
+        <v>16</v>
       </c>
       <c r="C87" s="7">
+        <v>12.6</v>
+      </c>
+      <c r="D87" s="7">
         <v>16</v>
       </c>
-      <c r="D87" s="7">
-        <v>16.100000000000001</v>
-      </c>
       <c r="E87" s="7">
-        <v>11.82</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F87" s="10">
-        <v>1.3</v>
+        <v>-3.4</v>
       </c>
       <c r="G87" s="10">
-        <v>8.84</v>
+        <v>-21.25</v>
       </c>
       <c r="H87" s="9">
-        <v>0.73</v>
-      </c>
-      <c r="I87" s="10">
-        <v>29.5</v>
+        <v>0.89100000000000001</v>
+      </c>
+      <c r="I87" s="8">
+        <v>22</v>
       </c>
       <c r="J87" s="8">
-        <v>-2.8</v>
+        <v>54.4</v>
       </c>
       <c r="K87" s="9">
-        <v>5.52</v>
+        <v>6.41</v>
       </c>
       <c r="L87" s="8">
-        <v>-3.8</v>
+        <v>1.51</v>
       </c>
       <c r="M87" s="9" t="s">
         <v>17</v>
@@ -5779,40 +5787,40 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>39630</v>
+        <v>39661</v>
       </c>
       <c r="B88" s="7">
-        <v>14.15</v>
+        <v>14.7</v>
       </c>
       <c r="C88" s="7">
-        <v>14.7</v>
+        <v>16</v>
       </c>
       <c r="D88" s="7">
-        <v>15.2</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="E88" s="7">
-        <v>12.1</v>
-      </c>
-      <c r="F88" s="10">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G88" s="10">
-        <v>3.89</v>
+        <v>11.82</v>
+      </c>
+      <c r="F88" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="G88" s="8">
+        <v>8.84</v>
       </c>
       <c r="H88" s="9">
-        <v>0.56399999999999995</v>
+        <v>0.73</v>
       </c>
       <c r="I88" s="8">
-        <v>-18.100000000000001</v>
-      </c>
-      <c r="J88" s="8">
-        <v>-26.4</v>
+        <v>29.5</v>
+      </c>
+      <c r="J88" s="10">
+        <v>-2.8</v>
       </c>
       <c r="K88" s="9">
-        <v>4.79</v>
-      </c>
-      <c r="L88" s="8">
-        <v>-3.95</v>
+        <v>5.52</v>
+      </c>
+      <c r="L88" s="10">
+        <v>-3.8</v>
       </c>
       <c r="M88" s="9" t="s">
         <v>17</v>
@@ -5832,40 +5840,40 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>39600</v>
+        <v>39630</v>
       </c>
       <c r="B89" s="7">
-        <v>16.399999999999999</v>
+        <v>14.15</v>
       </c>
       <c r="C89" s="7">
-        <v>14.15</v>
+        <v>14.7</v>
       </c>
       <c r="D89" s="7">
-        <v>16.399999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="E89" s="7">
-        <v>14.15</v>
+        <v>12.1</v>
       </c>
       <c r="F89" s="8">
-        <v>-2.25</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G89" s="8">
-        <v>-13.72</v>
+        <v>3.89</v>
       </c>
       <c r="H89" s="9">
-        <v>0.68799999999999994</v>
-      </c>
-      <c r="I89" s="8">
-        <v>-24.3</v>
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="I89" s="10">
+        <v>-18.100000000000001</v>
       </c>
       <c r="J89" s="10">
-        <v>6.14</v>
+        <v>-26.4</v>
       </c>
       <c r="K89" s="9">
-        <v>4.2300000000000004</v>
+        <v>4.79</v>
       </c>
       <c r="L89" s="10">
-        <v>0.11</v>
+        <v>-3.95</v>
       </c>
       <c r="M89" s="9" t="s">
         <v>17</v>
@@ -5885,40 +5893,40 @@
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>39569</v>
+        <v>39600</v>
       </c>
       <c r="B90" s="7">
-        <v>15</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="C90" s="7">
+        <v>14.15</v>
+      </c>
+      <c r="D90" s="7">
         <v>16.399999999999999</v>
       </c>
-      <c r="D90" s="7">
-        <v>16.5</v>
-      </c>
       <c r="E90" s="7">
-        <v>14</v>
+        <v>14.15</v>
       </c>
       <c r="F90" s="10">
-        <v>1.4</v>
+        <v>-2.25</v>
       </c>
       <c r="G90" s="10">
-        <v>9.33</v>
+        <v>-13.72</v>
       </c>
       <c r="H90" s="9">
-        <v>0.91</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="I90" s="10">
-        <v>22</v>
+        <v>-24.3</v>
       </c>
       <c r="J90" s="8">
-        <v>-12</v>
+        <v>6.14</v>
       </c>
       <c r="K90" s="9">
-        <v>3.54</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="L90" s="8">
-        <v>-0.98</v>
+        <v>0.11</v>
       </c>
       <c r="M90" s="9" t="s">
         <v>17</v>
@@ -5938,40 +5946,40 @@
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>39539</v>
+        <v>39569</v>
       </c>
       <c r="B91" s="7">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="C91" s="7">
-        <v>15</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D91" s="7">
-        <v>15.4</v>
+        <v>16.5</v>
       </c>
       <c r="E91" s="7">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="F91" s="8">
-        <v>-0.1</v>
+        <v>1.4</v>
       </c>
       <c r="G91" s="8">
-        <v>-0.66</v>
+        <v>9.33</v>
       </c>
       <c r="H91" s="9">
-        <v>0.745</v>
-      </c>
-      <c r="I91" s="10">
-        <v>14.5</v>
-      </c>
-      <c r="J91" s="8">
-        <v>-14</v>
+        <v>0.91</v>
+      </c>
+      <c r="I91" s="8">
+        <v>22</v>
+      </c>
+      <c r="J91" s="10">
+        <v>-12</v>
       </c>
       <c r="K91" s="9">
-        <v>2.63</v>
+        <v>3.54</v>
       </c>
       <c r="L91" s="10">
-        <v>3.5</v>
+        <v>-0.98</v>
       </c>
       <c r="M91" s="9" t="s">
         <v>17</v>
@@ -5991,40 +5999,40 @@
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>39508</v>
+        <v>39539</v>
       </c>
       <c r="B92" s="7">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="C92" s="7">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="D92" s="7">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="E92" s="7">
-        <v>14.2</v>
+        <v>14.33</v>
       </c>
       <c r="F92" s="10">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="G92" s="10">
-        <v>2.0299999999999998</v>
+        <v>-0.66</v>
       </c>
       <c r="H92" s="9">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="I92" s="10">
-        <v>28.1</v>
-      </c>
-      <c r="J92" s="8">
-        <v>-16.8</v>
+        <v>0.745</v>
+      </c>
+      <c r="I92" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="J92" s="10">
+        <v>-14</v>
       </c>
       <c r="K92" s="9">
-        <v>1.89</v>
-      </c>
-      <c r="L92" s="10">
-        <v>12.6</v>
+        <v>2.63</v>
+      </c>
+      <c r="L92" s="8">
+        <v>3.5</v>
       </c>
       <c r="M92" s="9" t="s">
         <v>17</v>
@@ -6044,40 +6052,40 @@
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>39479</v>
+        <v>39508</v>
       </c>
       <c r="B93" s="7">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="C93" s="7">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="D93" s="7">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="E93" s="7">
-        <v>13.6</v>
-      </c>
-      <c r="F93" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="G93" s="10">
-        <v>5.71</v>
+        <v>14.2</v>
+      </c>
+      <c r="F93" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="G93" s="8">
+        <v>2.0299999999999998</v>
       </c>
       <c r="H93" s="9">
-        <v>0.50800000000000001</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="I93" s="8">
-        <v>-30</v>
+        <v>28.1</v>
       </c>
       <c r="J93" s="10">
-        <v>51.9</v>
+        <v>-16.8</v>
       </c>
       <c r="K93" s="9">
-        <v>1.23</v>
-      </c>
-      <c r="L93" s="10">
-        <v>38.4</v>
+        <v>1.89</v>
+      </c>
+      <c r="L93" s="8">
+        <v>12.6</v>
       </c>
       <c r="M93" s="9" t="s">
         <v>17</v>
@@ -6097,40 +6105,40 @@
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>39448</v>
+        <v>39479</v>
       </c>
       <c r="B94" s="7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="C94" s="7">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="D94" s="7">
         <v>15</v>
       </c>
       <c r="E94" s="7">
-        <v>13.58</v>
+        <v>13.6</v>
       </c>
       <c r="F94" s="8">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G94" s="8">
-        <v>-3.45</v>
+        <v>5.71</v>
       </c>
       <c r="H94" s="9">
-        <v>0.72599999999999998</v>
-      </c>
-      <c r="I94" s="8">
-        <v>-14.7</v>
-      </c>
-      <c r="J94" s="10">
-        <v>30.2</v>
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="I94" s="10">
+        <v>-30</v>
+      </c>
+      <c r="J94" s="8">
+        <v>51.9</v>
       </c>
       <c r="K94" s="9">
-        <v>0.72599999999999998</v>
-      </c>
-      <c r="L94" s="10">
-        <v>30.2</v>
+        <v>1.23</v>
+      </c>
+      <c r="L94" s="8">
+        <v>38.4</v>
       </c>
       <c r="M94" s="9" t="s">
         <v>17</v>
@@ -6150,40 +6158,40 @@
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>39417</v>
+        <v>39448</v>
       </c>
       <c r="B95" s="7">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="C95" s="7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D95" s="7">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="E95" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="F95" s="8">
-        <v>-0.6</v>
-      </c>
-      <c r="G95" s="8">
-        <v>-3.97</v>
+        <v>13.58</v>
+      </c>
+      <c r="F95" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G95" s="10">
+        <v>-3.45</v>
       </c>
       <c r="H95" s="9">
-        <v>0.85099999999999998</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="I95" s="10">
-        <v>14.8</v>
-      </c>
-      <c r="J95" s="10">
-        <v>56.4</v>
+        <v>-14.7</v>
+      </c>
+      <c r="J95" s="8">
+        <v>30.2</v>
       </c>
       <c r="K95" s="9">
-        <v>8.94</v>
-      </c>
-      <c r="L95" s="10">
-        <v>0.82</v>
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="L95" s="8">
+        <v>30.2</v>
       </c>
       <c r="M95" s="9" t="s">
         <v>17</v>
@@ -6203,40 +6211,40 @@
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>39387</v>
+        <v>39417</v>
       </c>
       <c r="B96" s="7">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="C96" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="D96" s="7">
         <v>15.1</v>
-      </c>
-      <c r="D96" s="7">
-        <v>16.100000000000001</v>
       </c>
       <c r="E96" s="7">
         <v>13.5</v>
       </c>
       <c r="F96" s="10">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G96" s="10">
-        <v>0.67</v>
+        <v>-3.97</v>
       </c>
       <c r="H96" s="9">
-        <v>0.74199999999999999</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="I96" s="8">
-        <v>-27.9</v>
-      </c>
-      <c r="J96" s="10">
-        <v>19.3</v>
+        <v>14.8</v>
+      </c>
+      <c r="J96" s="8">
+        <v>56.4</v>
       </c>
       <c r="K96" s="9">
-        <v>8.09</v>
+        <v>8.94</v>
       </c>
       <c r="L96" s="8">
-        <v>-2.8</v>
+        <v>0.82</v>
       </c>
       <c r="M96" s="9" t="s">
         <v>17</v>
@@ -6256,40 +6264,40 @@
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>39356</v>
+        <v>39387</v>
       </c>
       <c r="B97" s="7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="C97" s="7">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="D97" s="7">
-        <v>16.2</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="E97" s="7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="F97" s="8">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G97" s="8">
-        <v>-3.23</v>
+        <v>0.67</v>
       </c>
       <c r="H97" s="9">
-        <v>1.03</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="I97" s="10">
-        <v>78.3</v>
-      </c>
-      <c r="J97" s="10">
-        <v>9.49</v>
+        <v>-27.9</v>
+      </c>
+      <c r="J97" s="8">
+        <v>19.3</v>
       </c>
       <c r="K97" s="9">
-        <v>7.35</v>
-      </c>
-      <c r="L97" s="8">
-        <v>-4.59</v>
+        <v>8.09</v>
+      </c>
+      <c r="L97" s="10">
+        <v>-2.8</v>
       </c>
       <c r="M97" s="9" t="s">
         <v>17</v>
@@ -6309,40 +6317,40 @@
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>39326</v>
+        <v>39356</v>
       </c>
       <c r="B98" s="7">
         <v>15.5</v>
       </c>
       <c r="C98" s="7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D98" s="7">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="E98" s="7">
-        <v>14.7</v>
-      </c>
-      <c r="F98" s="9">
-        <v>0</v>
-      </c>
-      <c r="G98" s="9">
-        <v>0</v>
+        <v>14.5</v>
+      </c>
+      <c r="F98" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G98" s="10">
+        <v>-3.23</v>
       </c>
       <c r="H98" s="9">
-        <v>0.57699999999999996</v>
+        <v>1.03</v>
       </c>
       <c r="I98" s="8">
-        <v>-23.2</v>
+        <v>78.3</v>
       </c>
       <c r="J98" s="8">
-        <v>-11.6</v>
+        <v>9.49</v>
       </c>
       <c r="K98" s="9">
-        <v>6.32</v>
-      </c>
-      <c r="L98" s="8">
-        <v>-6.54</v>
+        <v>7.35</v>
+      </c>
+      <c r="L98" s="10">
+        <v>-4.59</v>
       </c>
       <c r="M98" s="9" t="s">
         <v>17</v>
@@ -6362,40 +6370,40 @@
     </row>
     <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>39295</v>
+        <v>39326</v>
       </c>
       <c r="B99" s="7">
-        <v>16.600000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="C99" s="7">
         <v>15.5</v>
       </c>
       <c r="D99" s="7">
-        <v>17.600000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="E99" s="7">
-        <v>13</v>
-      </c>
-      <c r="F99" s="8">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="G99" s="8">
-        <v>-6.63</v>
+        <v>14.7</v>
+      </c>
+      <c r="F99" s="9">
+        <v>0</v>
+      </c>
+      <c r="G99" s="9">
+        <v>0</v>
       </c>
       <c r="H99" s="9">
-        <v>0.751</v>
-      </c>
-      <c r="I99" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="J99" s="8">
-        <v>-22.6</v>
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="I99" s="10">
+        <v>-23.2</v>
+      </c>
+      <c r="J99" s="10">
+        <v>-11.6</v>
       </c>
       <c r="K99" s="9">
-        <v>5.74</v>
-      </c>
-      <c r="L99" s="8">
-        <v>-6.01</v>
+        <v>6.32</v>
+      </c>
+      <c r="L99" s="10">
+        <v>-6.54</v>
       </c>
       <c r="M99" s="9" t="s">
         <v>17</v>
@@ -6415,40 +6423,40 @@
     </row>
     <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>39264</v>
+        <v>39295</v>
       </c>
       <c r="B100" s="7">
-        <v>14.3</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="C100" s="7">
-        <v>16.600000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="D100" s="7">
-        <v>18.600000000000001</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E100" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F100" s="10">
-        <v>2.2999999999999998</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="G100" s="10">
-        <v>16.079999999999998</v>
+        <v>-6.63</v>
       </c>
       <c r="H100" s="9">
-        <v>0.76600000000000001</v>
+        <v>0.751</v>
       </c>
       <c r="I100" s="10">
-        <v>18</v>
-      </c>
-      <c r="J100" s="8">
-        <v>-8.25</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J100" s="10">
+        <v>-22.6</v>
       </c>
       <c r="K100" s="9">
-        <v>4.99</v>
-      </c>
-      <c r="L100" s="8">
-        <v>-2.88</v>
+        <v>5.74</v>
+      </c>
+      <c r="L100" s="10">
+        <v>-6.01</v>
       </c>
       <c r="M100" s="9" t="s">
         <v>17</v>
@@ -6468,40 +6476,40 @@
     </row>
     <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>39234</v>
+        <v>39264</v>
       </c>
       <c r="B101" s="7">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="C101" s="7">
-        <v>14.3</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D101" s="7">
-        <v>15.5</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="E101" s="7">
-        <v>11.45</v>
-      </c>
-      <c r="F101" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="G101" s="10">
-        <v>10.85</v>
+        <v>14</v>
+      </c>
+      <c r="F101" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G101" s="8">
+        <v>16.079999999999998</v>
       </c>
       <c r="H101" s="9">
-        <v>0.64900000000000002</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="I101" s="8">
-        <v>-37.299999999999997</v>
-      </c>
-      <c r="J101" s="8">
-        <v>-20.2</v>
+        <v>18</v>
+      </c>
+      <c r="J101" s="10">
+        <v>-8.25</v>
       </c>
       <c r="K101" s="9">
-        <v>4.22</v>
-      </c>
-      <c r="L101" s="8">
-        <v>-1.83</v>
+        <v>4.99</v>
+      </c>
+      <c r="L101" s="10">
+        <v>-2.88</v>
       </c>
       <c r="M101" s="9" t="s">
         <v>17</v>
@@ -6521,40 +6529,40 @@
     </row>
     <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>39203</v>
+        <v>39234</v>
       </c>
       <c r="B102" s="7">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="C102" s="7">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="D102" s="7">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="E102" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="F102" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G102" s="10">
-        <v>2.38</v>
+        <v>11.45</v>
+      </c>
+      <c r="F102" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="G102" s="8">
+        <v>10.85</v>
       </c>
       <c r="H102" s="9">
-        <v>1.03</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="I102" s="10">
-        <v>19.2</v>
+        <v>-37.299999999999997</v>
       </c>
       <c r="J102" s="10">
-        <v>35.1</v>
+        <v>-20.2</v>
       </c>
       <c r="K102" s="9">
-        <v>3.58</v>
+        <v>4.22</v>
       </c>
       <c r="L102" s="10">
-        <v>2.44</v>
+        <v>-1.83</v>
       </c>
       <c r="M102" s="9" t="s">
         <v>17</v>
@@ -6574,40 +6582,40 @@
     </row>
     <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>39173</v>
+        <v>39203</v>
       </c>
       <c r="B103" s="7">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="C103" s="7">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="D103" s="7">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="E103" s="7">
-        <v>11</v>
-      </c>
-      <c r="F103" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="G103" s="10">
-        <v>11.5</v>
+        <v>12.3</v>
+      </c>
+      <c r="F103" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="G103" s="8">
+        <v>2.38</v>
       </c>
       <c r="H103" s="9">
-        <v>0.86699999999999999</v>
-      </c>
-      <c r="I103" s="10">
-        <v>10.8</v>
-      </c>
-      <c r="J103" s="10">
-        <v>22</v>
+        <v>1.03</v>
+      </c>
+      <c r="I103" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="J103" s="8">
+        <v>35.1</v>
       </c>
       <c r="K103" s="9">
-        <v>2.54</v>
+        <v>3.58</v>
       </c>
       <c r="L103" s="8">
-        <v>-6.73</v>
+        <v>2.44</v>
       </c>
       <c r="M103" s="9" t="s">
         <v>17</v>
@@ -6627,40 +6635,40 @@
     </row>
     <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>39142</v>
+        <v>39173</v>
       </c>
       <c r="B104" s="7">
-        <v>10.96</v>
+        <v>11.3</v>
       </c>
       <c r="C104" s="7">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="D104" s="7">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="E104" s="7">
+        <v>11</v>
+      </c>
+      <c r="F104" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="G104" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="H104" s="9">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="I104" s="8">
         <v>10.8</v>
       </c>
-      <c r="F104" s="10">
-        <v>0.34</v>
-      </c>
-      <c r="G104" s="10">
-        <v>3.1</v>
-      </c>
-      <c r="H104" s="9">
-        <v>0.78300000000000003</v>
-      </c>
-      <c r="I104" s="10">
-        <v>133.80000000000001</v>
-      </c>
       <c r="J104" s="8">
-        <v>-37.4</v>
+        <v>22</v>
       </c>
       <c r="K104" s="9">
-        <v>1.67</v>
-      </c>
-      <c r="L104" s="8">
-        <v>-16.899999999999999</v>
+        <v>2.54</v>
+      </c>
+      <c r="L104" s="10">
+        <v>-6.73</v>
       </c>
       <c r="M104" s="9" t="s">
         <v>17</v>
@@ -6680,40 +6688,40 @@
     </row>
     <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>39114</v>
+        <v>39142</v>
       </c>
       <c r="B105" s="7">
-        <v>11.15</v>
+        <v>10.96</v>
       </c>
       <c r="C105" s="7">
-        <v>10.96</v>
+        <v>11.3</v>
       </c>
       <c r="D105" s="7">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="E105" s="7">
         <v>10.8</v>
       </c>
       <c r="F105" s="8">
-        <v>-0.19</v>
+        <v>0.34</v>
       </c>
       <c r="G105" s="8">
-        <v>-1.7</v>
+        <v>3.1</v>
       </c>
       <c r="H105" s="9">
-        <v>0.33500000000000002</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="I105" s="8">
-        <v>-40</v>
-      </c>
-      <c r="J105" s="8">
-        <v>-20.6</v>
+        <v>133.80000000000001</v>
+      </c>
+      <c r="J105" s="10">
+        <v>-37.4</v>
       </c>
       <c r="K105" s="9">
-        <v>0.89200000000000002</v>
+        <v>1.67</v>
       </c>
       <c r="L105" s="10">
-        <v>16.8</v>
+        <v>-16.899999999999999</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>17</v>
@@ -6733,40 +6741,40 @@
     </row>
     <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>39083</v>
+        <v>39114</v>
       </c>
       <c r="B106" s="7">
-        <v>11.1</v>
+        <v>11.15</v>
       </c>
       <c r="C106" s="7">
-        <v>11.15</v>
+        <v>10.96</v>
       </c>
       <c r="D106" s="7">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="E106" s="7">
         <v>10.8</v>
       </c>
       <c r="F106" s="10">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="G106" s="10">
-        <v>0.45</v>
+        <v>-1.7</v>
       </c>
       <c r="H106" s="9">
-        <v>0.55700000000000005</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="I106" s="10">
-        <v>2.44</v>
+        <v>-40</v>
       </c>
       <c r="J106" s="10">
-        <v>62.9</v>
+        <v>-20.6</v>
       </c>
       <c r="K106" s="9">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="L106" s="10">
-        <v>62.9</v>
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="L106" s="8">
+        <v>16.8</v>
       </c>
       <c r="M106" s="9" t="s">
         <v>17</v>
@@ -6786,40 +6794,40 @@
     </row>
     <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>39052</v>
+        <v>39083</v>
       </c>
       <c r="B107" s="7">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="C107" s="7">
-        <v>11.1</v>
+        <v>11.15</v>
       </c>
       <c r="D107" s="7">
         <v>11.5</v>
       </c>
       <c r="E107" s="7">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="F107" s="8">
-        <v>-0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G107" s="8">
-        <v>-1.77</v>
+        <v>0.45</v>
       </c>
       <c r="H107" s="9">
-        <v>0.54400000000000004</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="I107" s="8">
-        <v>-12.5</v>
+        <v>2.44</v>
       </c>
       <c r="J107" s="8">
-        <v>-20.5</v>
+        <v>62.9</v>
       </c>
       <c r="K107" s="9">
-        <v>8.86</v>
-      </c>
-      <c r="L107" s="10">
-        <v>4.47</v>
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="L107" s="8">
+        <v>62.9</v>
       </c>
       <c r="M107" s="9" t="s">
         <v>17</v>
@@ -6839,40 +6847,40 @@
     </row>
     <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>39022</v>
+        <v>39052</v>
       </c>
       <c r="B108" s="7">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="C108" s="7">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="D108" s="7">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="E108" s="7">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="F108" s="10">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="G108" s="10">
-        <v>6.6</v>
+        <v>-1.77</v>
       </c>
       <c r="H108" s="9">
-        <v>0.622</v>
-      </c>
-      <c r="I108" s="8">
-        <v>-33.799999999999997</v>
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="I108" s="10">
+        <v>-12.5</v>
       </c>
       <c r="J108" s="10">
-        <v>30</v>
+        <v>-20.5</v>
       </c>
       <c r="K108" s="9">
-        <v>8.32</v>
-      </c>
-      <c r="L108" s="10">
-        <v>6.66</v>
+        <v>8.86</v>
+      </c>
+      <c r="L108" s="8">
+        <v>4.47</v>
       </c>
       <c r="M108" s="9" t="s">
         <v>17</v>
@@ -6892,40 +6900,40 @@
     </row>
     <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>38991</v>
+        <v>39022</v>
       </c>
       <c r="B109" s="7">
-        <v>9.85</v>
+        <v>10.6</v>
       </c>
       <c r="C109" s="7">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="D109" s="7">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="E109" s="7">
-        <v>9.85</v>
-      </c>
-      <c r="F109" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="G109" s="10">
-        <v>7.61</v>
+        <v>9.9</v>
+      </c>
+      <c r="F109" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="G109" s="8">
+        <v>6.6</v>
       </c>
       <c r="H109" s="9">
-        <v>0.93899999999999995</v>
+        <v>0.622</v>
       </c>
       <c r="I109" s="10">
-        <v>44</v>
-      </c>
-      <c r="J109" s="10">
-        <v>23.2</v>
+        <v>-33.799999999999997</v>
+      </c>
+      <c r="J109" s="8">
+        <v>30</v>
       </c>
       <c r="K109" s="9">
-        <v>7.7</v>
-      </c>
-      <c r="L109" s="10">
-        <v>5.14</v>
+        <v>8.32</v>
+      </c>
+      <c r="L109" s="8">
+        <v>6.66</v>
       </c>
       <c r="M109" s="9" t="s">
         <v>17</v>
@@ -6945,40 +6953,40 @@
     </row>
     <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>38961</v>
+        <v>38991</v>
       </c>
       <c r="B110" s="7">
-        <v>10.4</v>
+        <v>9.85</v>
       </c>
       <c r="C110" s="7">
-        <v>9.85</v>
+        <v>10.6</v>
       </c>
       <c r="D110" s="7">
         <v>10.7</v>
       </c>
       <c r="E110" s="7">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="F110" s="8">
-        <v>-0.55000000000000004</v>
+        <v>0.75</v>
       </c>
       <c r="G110" s="8">
-        <v>-5.29</v>
+        <v>7.61</v>
       </c>
       <c r="H110" s="9">
-        <v>0.65200000000000002</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="I110" s="8">
-        <v>-32.799999999999997</v>
+        <v>44</v>
       </c>
       <c r="J110" s="8">
-        <v>-23.9</v>
+        <v>23.2</v>
       </c>
       <c r="K110" s="9">
-        <v>6.76</v>
-      </c>
-      <c r="L110" s="10">
-        <v>3.04</v>
+        <v>7.7</v>
+      </c>
+      <c r="L110" s="8">
+        <v>5.14</v>
       </c>
       <c r="M110" s="9" t="s">
         <v>17</v>
@@ -6998,40 +7006,40 @@
     </row>
     <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>38930</v>
+        <v>38961</v>
       </c>
       <c r="B111" s="7">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="C111" s="7">
-        <v>10.4</v>
+        <v>9.85</v>
       </c>
       <c r="D111" s="7">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="E111" s="7">
-        <v>9.8000000000000007</v>
+        <v>9.5</v>
       </c>
       <c r="F111" s="10">
-        <v>0.4</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="G111" s="10">
-        <v>4</v>
+        <v>-5.29</v>
       </c>
       <c r="H111" s="9">
-        <v>0.97</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="I111" s="10">
-        <v>16.3</v>
+        <v>-32.799999999999997</v>
       </c>
       <c r="J111" s="10">
-        <v>16</v>
+        <v>-23.9</v>
       </c>
       <c r="K111" s="9">
-        <v>6.11</v>
-      </c>
-      <c r="L111" s="10">
-        <v>7.1</v>
+        <v>6.76</v>
+      </c>
+      <c r="L111" s="8">
+        <v>3.04</v>
       </c>
       <c r="M111" s="9" t="s">
         <v>17</v>
@@ -7051,40 +7059,40 @@
     </row>
     <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>38899</v>
+        <v>38930</v>
       </c>
       <c r="B112" s="7">
+        <v>10</v>
+      </c>
+      <c r="C112" s="7">
         <v>10.4</v>
       </c>
-      <c r="C112" s="7">
-        <v>10</v>
-      </c>
       <c r="D112" s="7">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="E112" s="7">
-        <v>10</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F112" s="8">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="G112" s="8">
-        <v>-3.85</v>
+        <v>4</v>
       </c>
       <c r="H112" s="9">
-        <v>0.83399999999999996</v>
-      </c>
-      <c r="I112" s="10">
-        <v>2.62</v>
-      </c>
-      <c r="J112" s="10">
-        <v>18</v>
+        <v>0.97</v>
+      </c>
+      <c r="I112" s="8">
+        <v>16.3</v>
+      </c>
+      <c r="J112" s="8">
+        <v>16</v>
       </c>
       <c r="K112" s="9">
-        <v>5.14</v>
-      </c>
-      <c r="L112" s="10">
-        <v>5.57</v>
+        <v>6.11</v>
+      </c>
+      <c r="L112" s="8">
+        <v>7.1</v>
       </c>
       <c r="M112" s="9" t="s">
         <v>17</v>
@@ -7104,13 +7112,13 @@
     </row>
     <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>38869</v>
+        <v>38899</v>
       </c>
       <c r="B113" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="C113" s="7">
         <v>10</v>
-      </c>
-      <c r="C113" s="7">
-        <v>10.4</v>
       </c>
       <c r="D113" s="7">
         <v>10.4</v>
@@ -7119,25 +7127,25 @@
         <v>10</v>
       </c>
       <c r="F113" s="10">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G113" s="10">
-        <v>4</v>
+        <v>-3.85</v>
       </c>
       <c r="H113" s="9">
-        <v>0.81299999999999994</v>
-      </c>
-      <c r="I113" s="10">
-        <v>6.26</v>
-      </c>
-      <c r="J113" s="10">
-        <v>29.2</v>
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="I113" s="8">
+        <v>2.62</v>
+      </c>
+      <c r="J113" s="8">
+        <v>18</v>
       </c>
       <c r="K113" s="9">
-        <v>4.3</v>
-      </c>
-      <c r="L113" s="10">
-        <v>3.46</v>
+        <v>5.14</v>
+      </c>
+      <c r="L113" s="8">
+        <v>5.57</v>
       </c>
       <c r="M113" s="9" t="s">
         <v>17</v>
@@ -7157,40 +7165,40 @@
     </row>
     <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>38838</v>
+        <v>38869</v>
       </c>
       <c r="B114" s="7">
-        <v>10.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="C114" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="D114" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="E114" s="7">
         <v>10</v>
       </c>
-      <c r="D114" s="7">
-        <v>10.9</v>
-      </c>
-      <c r="E114" s="7">
-        <v>9.6999999999999993</v>
-      </c>
       <c r="F114" s="8">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G114" s="8">
-        <v>-1.96</v>
+        <v>4</v>
       </c>
       <c r="H114" s="9">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="I114" s="10">
-        <v>7.65</v>
-      </c>
-      <c r="J114" s="10">
-        <v>12.7</v>
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="I114" s="8">
+        <v>6.26</v>
+      </c>
+      <c r="J114" s="8">
+        <v>29.2</v>
       </c>
       <c r="K114" s="9">
-        <v>3.49</v>
+        <v>4.3</v>
       </c>
       <c r="L114" s="8">
-        <v>-1.1200000000000001</v>
+        <v>3.46</v>
       </c>
       <c r="M114" s="9" t="s">
         <v>17</v>
@@ -7210,40 +7218,40 @@
     </row>
     <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>38808</v>
+        <v>38838</v>
       </c>
       <c r="B115" s="7">
-        <v>9.3000000000000007</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C115" s="7">
-        <v>10.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="D115" s="7">
-        <v>10.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="E115" s="7">
-        <v>9.3000000000000007</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F115" s="10">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="G115" s="10">
-        <v>9.68</v>
+        <v>-1.96</v>
       </c>
       <c r="H115" s="9">
-        <v>0.71099999999999997</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="I115" s="8">
-        <v>-43.2</v>
+        <v>7.65</v>
       </c>
       <c r="J115" s="8">
-        <v>-21.6</v>
+        <v>12.7</v>
       </c>
       <c r="K115" s="9">
-        <v>2.73</v>
-      </c>
-      <c r="L115" s="8">
-        <v>-4.42</v>
+        <v>3.49</v>
+      </c>
+      <c r="L115" s="10">
+        <v>-1.1200000000000001</v>
       </c>
       <c r="M115" s="9" t="s">
         <v>17</v>
@@ -7263,40 +7271,40 @@
     </row>
     <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>38777</v>
+        <v>38808</v>
       </c>
       <c r="B116" s="7">
-        <v>9.4</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C116" s="7">
-        <v>9.3000000000000007</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D116" s="7">
-        <v>10.4</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E116" s="7">
         <v>9.3000000000000007</v>
       </c>
       <c r="F116" s="8">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="G116" s="8">
-        <v>-1.06</v>
+        <v>9.68</v>
       </c>
       <c r="H116" s="9">
-        <v>1.25</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="I116" s="10">
-        <v>196.6</v>
+        <v>-43.2</v>
       </c>
       <c r="J116" s="10">
-        <v>77.599999999999994</v>
+        <v>-21.6</v>
       </c>
       <c r="K116" s="9">
-        <v>2.0099999999999998</v>
+        <v>2.73</v>
       </c>
       <c r="L116" s="10">
-        <v>3.61</v>
+        <v>-4.42</v>
       </c>
       <c r="M116" s="9" t="s">
         <v>17</v>
@@ -7316,40 +7324,40 @@
     </row>
     <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>38749</v>
+        <v>38777</v>
       </c>
       <c r="B117" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="C117" s="7">
         <v>9.3000000000000007</v>
       </c>
-      <c r="C117" s="7">
-        <v>9.4</v>
-      </c>
       <c r="D117" s="7">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="E117" s="7">
-        <v>9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F117" s="10">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="G117" s="10">
-        <v>1.08</v>
+        <v>-1.06</v>
       </c>
       <c r="H117" s="9">
-        <v>0.42199999999999999</v>
-      </c>
-      <c r="I117" s="10">
-        <v>23.3</v>
+        <v>1.25</v>
+      </c>
+      <c r="I117" s="8">
+        <v>196.6</v>
       </c>
       <c r="J117" s="8">
-        <v>-21.2</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="K117" s="9">
-        <v>0.76400000000000001</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="L117" s="8">
-        <v>-38.4</v>
+        <v>3.61</v>
       </c>
       <c r="M117" s="9" t="s">
         <v>17</v>
@@ -7369,40 +7377,40 @@
     </row>
     <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>38718</v>
+        <v>38749</v>
       </c>
       <c r="B118" s="7">
-        <v>9.6</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C118" s="7">
-        <v>9.3000000000000007</v>
+        <v>9.4</v>
       </c>
       <c r="D118" s="7">
-        <v>9.85</v>
+        <v>9.4</v>
       </c>
       <c r="E118" s="7">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F118" s="8">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G118" s="8">
-        <v>-3.12</v>
+        <v>1.08</v>
       </c>
       <c r="H118" s="9">
-        <v>0.34200000000000003</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="I118" s="8">
-        <v>-50</v>
-      </c>
-      <c r="J118" s="8">
-        <v>-51.5</v>
+        <v>23.3</v>
+      </c>
+      <c r="J118" s="10">
+        <v>-21.2</v>
       </c>
       <c r="K118" s="9">
-        <v>0.34200000000000003</v>
-      </c>
-      <c r="L118" s="8">
-        <v>-51.5</v>
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="L118" s="10">
+        <v>-38.4</v>
       </c>
       <c r="M118" s="9" t="s">
         <v>17</v>
@@ -7422,40 +7430,40 @@
     </row>
     <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>38687</v>
+        <v>38718</v>
       </c>
       <c r="B119" s="7">
-        <v>9.1999999999999993</v>
+        <v>9.6</v>
       </c>
       <c r="C119" s="7">
-        <v>9.6</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D119" s="7">
-        <v>10</v>
+        <v>9.85</v>
       </c>
       <c r="E119" s="7">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="F119" s="10">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="G119" s="10">
-        <v>4.3499999999999996</v>
+        <v>-3.12</v>
       </c>
       <c r="H119" s="9">
-        <v>0.68500000000000005</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="I119" s="10">
-        <v>43.2</v>
-      </c>
-      <c r="J119" s="8">
-        <v>-31.5</v>
+        <v>-50</v>
+      </c>
+      <c r="J119" s="10">
+        <v>-51.5</v>
       </c>
       <c r="K119" s="9">
-        <v>8.49</v>
-      </c>
-      <c r="L119" s="8">
-        <v>-4.87</v>
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="L119" s="10">
+        <v>-51.5</v>
       </c>
       <c r="M119" s="9" t="s">
         <v>17</v>
@@ -7475,40 +7483,40 @@
     </row>
     <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>38657</v>
+        <v>38687</v>
       </c>
       <c r="B120" s="7">
-        <v>10.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="C120" s="7">
-        <v>9.1999999999999993</v>
+        <v>9.6</v>
       </c>
       <c r="D120" s="7">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="E120" s="7">
-        <v>9.1999999999999993</v>
+        <v>9.1</v>
       </c>
       <c r="F120" s="8">
-        <v>-1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G120" s="8">
-        <v>-14.02</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H120" s="9">
-        <v>0.47799999999999998</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="I120" s="8">
-        <v>-37.299999999999997</v>
-      </c>
-      <c r="J120" s="8">
-        <v>-40</v>
+        <v>43.2</v>
+      </c>
+      <c r="J120" s="10">
+        <v>-31.5</v>
       </c>
       <c r="K120" s="9">
-        <v>7.8</v>
-      </c>
-      <c r="L120" s="8">
-        <v>-1.51</v>
+        <v>8.49</v>
+      </c>
+      <c r="L120" s="10">
+        <v>-4.87</v>
       </c>
       <c r="M120" s="9" t="s">
         <v>17</v>
@@ -7528,40 +7536,40 @@
     </row>
     <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>38626</v>
+        <v>38657</v>
       </c>
       <c r="B121" s="7">
         <v>10.7</v>
       </c>
       <c r="C121" s="7">
-        <v>10.7</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D121" s="7">
         <v>10.7</v>
       </c>
       <c r="E121" s="7">
-        <v>10.1</v>
-      </c>
-      <c r="F121" s="9">
-        <v>0</v>
-      </c>
-      <c r="G121" s="9">
-        <v>0</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F121" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G121" s="10">
+        <v>-14.02</v>
       </c>
       <c r="H121" s="9">
-        <v>0.76200000000000001</v>
-      </c>
-      <c r="I121" s="8">
-        <v>-11.1</v>
-      </c>
-      <c r="J121" s="8">
-        <v>-8.1</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="I121" s="10">
+        <v>-37.299999999999997</v>
+      </c>
+      <c r="J121" s="10">
+        <v>-40</v>
       </c>
       <c r="K121" s="9">
-        <v>7.32</v>
+        <v>7.8</v>
       </c>
       <c r="L121" s="10">
-        <v>2.8</v>
+        <v>-1.51</v>
       </c>
       <c r="M121" s="9" t="s">
         <v>17</v>
@@ -7581,40 +7589,40 @@
     </row>
     <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>38596</v>
+        <v>38626</v>
       </c>
       <c r="B122" s="7">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="C122" s="7">
         <v>10.7</v>
       </c>
       <c r="D122" s="7">
-        <v>11.65</v>
+        <v>10.7</v>
       </c>
       <c r="E122" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="F122" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="G122" s="10">
-        <v>0.94</v>
+        <v>10.1</v>
+      </c>
+      <c r="F122" s="9">
+        <v>0</v>
+      </c>
+      <c r="G122" s="9">
+        <v>0</v>
       </c>
       <c r="H122" s="9">
-        <v>0.85699999999999998</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="I122" s="10">
-        <v>2.54</v>
+        <v>-11.1</v>
       </c>
       <c r="J122" s="10">
-        <v>61.2</v>
+        <v>-8.1</v>
       </c>
       <c r="K122" s="9">
-        <v>6.56</v>
-      </c>
-      <c r="L122" s="10">
-        <v>4.24</v>
+        <v>7.32</v>
+      </c>
+      <c r="L122" s="8">
+        <v>2.8</v>
       </c>
       <c r="M122" s="9" t="s">
         <v>17</v>
@@ -7634,40 +7642,40 @@
     </row>
     <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>38565</v>
+        <v>38596</v>
       </c>
       <c r="B123" s="7">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="C123" s="7">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="D123" s="7">
-        <v>10.6</v>
+        <v>11.65</v>
       </c>
       <c r="E123" s="7">
-        <v>10</v>
-      </c>
-      <c r="F123" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G123" s="10">
-        <v>6</v>
+        <v>10.5</v>
+      </c>
+      <c r="F123" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G123" s="8">
+        <v>0.94</v>
       </c>
       <c r="H123" s="9">
-        <v>0.83599999999999997</v>
-      </c>
-      <c r="I123" s="10">
-        <v>18.2</v>
-      </c>
-      <c r="J123" s="10">
-        <v>6.63</v>
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="I123" s="8">
+        <v>2.54</v>
+      </c>
+      <c r="J123" s="8">
+        <v>61.2</v>
       </c>
       <c r="K123" s="9">
-        <v>5.7</v>
+        <v>6.56</v>
       </c>
       <c r="L123" s="8">
-        <v>-1.01</v>
+        <v>4.24</v>
       </c>
       <c r="M123" s="9" t="s">
         <v>17</v>
@@ -7687,40 +7695,40 @@
     </row>
     <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>38534</v>
+        <v>38565</v>
       </c>
       <c r="B124" s="7">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="C124" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="D124" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="E124" s="7">
         <v>10</v>
       </c>
-      <c r="D124" s="7">
-        <v>10.3</v>
-      </c>
-      <c r="E124" s="7">
-        <v>9.5</v>
-      </c>
       <c r="F124" s="8">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G124" s="8">
-        <v>-2.91</v>
+        <v>6</v>
       </c>
       <c r="H124" s="9">
-        <v>0.70699999999999996</v>
-      </c>
-      <c r="I124" s="10">
-        <v>12.4</v>
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="I124" s="8">
+        <v>18.2</v>
       </c>
       <c r="J124" s="8">
-        <v>-14.2</v>
+        <v>6.63</v>
       </c>
       <c r="K124" s="9">
-        <v>4.87</v>
-      </c>
-      <c r="L124" s="8">
-        <v>-2.2200000000000002</v>
+        <v>5.7</v>
+      </c>
+      <c r="L124" s="10">
+        <v>-1.01</v>
       </c>
       <c r="M124" s="9" t="s">
         <v>17</v>
@@ -7740,40 +7748,40 @@
     </row>
     <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>38504</v>
+        <v>38534</v>
       </c>
       <c r="B125" s="7">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="C125" s="7">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="D125" s="7">
         <v>10.3</v>
       </c>
       <c r="E125" s="7">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="F125" s="10">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="G125" s="10">
-        <v>1.98</v>
+        <v>-2.91</v>
       </c>
       <c r="H125" s="9">
-        <v>0.629</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="I125" s="8">
-        <v>-7.3</v>
-      </c>
-      <c r="J125" s="8">
-        <v>-21.7</v>
+        <v>12.4</v>
+      </c>
+      <c r="J125" s="10">
+        <v>-14.2</v>
       </c>
       <c r="K125" s="9">
-        <v>4.16</v>
+        <v>4.87</v>
       </c>
       <c r="L125" s="10">
-        <v>0.15</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="M125" s="9" t="s">
         <v>17</v>
@@ -7793,40 +7801,40 @@
     </row>
     <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>38473</v>
+        <v>38504</v>
       </c>
       <c r="B126" s="7">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="C126" s="7">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="D126" s="7">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="E126" s="7">
         <v>10</v>
       </c>
       <c r="F126" s="8">
-        <v>-0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G126" s="8">
-        <v>-6.48</v>
+        <v>1.98</v>
       </c>
       <c r="H126" s="9">
-        <v>0.67900000000000005</v>
-      </c>
-      <c r="I126" s="8">
-        <v>-25.2</v>
-      </c>
-      <c r="J126" s="8">
-        <v>-3.07</v>
+        <v>0.629</v>
+      </c>
+      <c r="I126" s="10">
+        <v>-7.3</v>
+      </c>
+      <c r="J126" s="10">
+        <v>-21.7</v>
       </c>
       <c r="K126" s="9">
-        <v>3.53</v>
-      </c>
-      <c r="L126" s="10">
-        <v>5.39</v>
+        <v>4.16</v>
+      </c>
+      <c r="L126" s="8">
+        <v>0.15</v>
       </c>
       <c r="M126" s="9" t="s">
         <v>17</v>
@@ -7846,13 +7854,13 @@
     </row>
     <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>38443</v>
+        <v>38473</v>
       </c>
       <c r="B127" s="7">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="C127" s="7">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="D127" s="7">
         <v>10.8</v>
@@ -7861,25 +7869,25 @@
         <v>10</v>
       </c>
       <c r="F127" s="10">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="G127" s="10">
-        <v>1.89</v>
+        <v>-6.48</v>
       </c>
       <c r="H127" s="9">
-        <v>0.90700000000000003</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="I127" s="10">
-        <v>28.8</v>
+        <v>-25.2</v>
       </c>
       <c r="J127" s="10">
-        <v>37.6</v>
+        <v>-3.07</v>
       </c>
       <c r="K127" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="L127" s="10">
-        <v>5.81</v>
+        <v>3.53</v>
+      </c>
+      <c r="L127" s="8">
+        <v>5.39</v>
       </c>
       <c r="M127" s="9" t="s">
         <v>17</v>
@@ -7899,40 +7907,40 @@
     </row>
     <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>38412</v>
+        <v>38443</v>
       </c>
       <c r="B128" s="7">
-        <v>11.5</v>
+        <v>10.6</v>
       </c>
       <c r="C128" s="7">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="D128" s="7">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="E128" s="7">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="F128" s="8">
-        <v>-0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G128" s="8">
-        <v>-7.83</v>
+        <v>1.89</v>
       </c>
       <c r="H128" s="9">
-        <v>0.70399999999999996</v>
-      </c>
-      <c r="I128" s="10">
-        <v>31.6</v>
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="I128" s="8">
+        <v>28.8</v>
       </c>
       <c r="J128" s="8">
-        <v>-14.8</v>
+        <v>37.6</v>
       </c>
       <c r="K128" s="9">
-        <v>1.94</v>
+        <v>2.85</v>
       </c>
       <c r="L128" s="8">
-        <v>-4.46</v>
+        <v>5.81</v>
       </c>
       <c r="M128" s="9" t="s">
         <v>17</v>
@@ -7952,40 +7960,40 @@
     </row>
     <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>38384</v>
+        <v>38412</v>
       </c>
       <c r="B129" s="7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="C129" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="D129" s="7">
         <v>11.5</v>
       </c>
-      <c r="D129" s="7">
-        <v>11.7</v>
-      </c>
       <c r="E129" s="7">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="F129" s="10">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="G129" s="10">
-        <v>4.55</v>
+        <v>-7.83</v>
       </c>
       <c r="H129" s="9">
-        <v>0.53500000000000003</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="I129" s="8">
-        <v>-24.1</v>
-      </c>
-      <c r="J129" s="8">
-        <v>-16</v>
+        <v>31.6</v>
+      </c>
+      <c r="J129" s="10">
+        <v>-14.8</v>
       </c>
       <c r="K129" s="9">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="L129" s="10">
-        <v>2.57</v>
+        <v>-4.46</v>
       </c>
       <c r="M129" s="9" t="s">
         <v>17</v>
@@ -8005,40 +8013,40 @@
     </row>
     <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>38353</v>
+        <v>38384</v>
       </c>
       <c r="B130" s="7">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="C130" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="D130" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="E130" s="7">
         <v>11</v>
       </c>
-      <c r="D130" s="7">
-        <v>11.2</v>
-      </c>
-      <c r="E130" s="7">
-        <v>10.9</v>
-      </c>
       <c r="F130" s="8">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G130" s="8">
-        <v>-1.79</v>
+        <v>4.55</v>
       </c>
       <c r="H130" s="9">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="I130" s="8">
-        <v>-29.5</v>
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="I130" s="10">
+        <v>-24.1</v>
       </c>
       <c r="J130" s="10">
-        <v>23.4</v>
+        <v>-16</v>
       </c>
       <c r="K130" s="9">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="L130" s="10">
-        <v>23.4</v>
+        <v>1.24</v>
+      </c>
+      <c r="L130" s="8">
+        <v>2.57</v>
       </c>
       <c r="M130" s="9" t="s">
         <v>17</v>
@@ -8058,40 +8066,40 @@
     </row>
     <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>38322</v>
+        <v>38353</v>
       </c>
       <c r="B131" s="7">
-        <v>11.05</v>
+        <v>11.2</v>
       </c>
       <c r="C131" s="7">
+        <v>11</v>
+      </c>
+      <c r="D131" s="7">
         <v>11.2</v>
       </c>
-      <c r="D131" s="7">
-        <v>11.5</v>
-      </c>
       <c r="E131" s="7">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="F131" s="10">
-        <v>0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="G131" s="10">
-        <v>1.36</v>
+        <v>-1.79</v>
       </c>
       <c r="H131" s="9">
-        <v>1</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="I131" s="10">
-        <v>25.4</v>
-      </c>
-      <c r="J131" s="10">
-        <v>39.6</v>
+        <v>-29.5</v>
+      </c>
+      <c r="J131" s="8">
+        <v>23.4</v>
       </c>
       <c r="K131" s="9">
-        <v>8.92</v>
-      </c>
-      <c r="L131" s="10">
-        <v>44.9</v>
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="L131" s="8">
+        <v>23.4</v>
       </c>
       <c r="M131" s="9" t="s">
         <v>17</v>
@@ -8111,40 +8119,40 @@
     </row>
     <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>38292</v>
+        <v>38322</v>
       </c>
       <c r="B132" s="7">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="C132" s="7">
-        <v>11.05</v>
+        <v>11.2</v>
       </c>
       <c r="D132" s="7">
         <v>11.5</v>
       </c>
       <c r="E132" s="7">
-        <v>10.95</v>
-      </c>
-      <c r="F132" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="G132" s="10">
-        <v>0.45</v>
+        <v>10</v>
+      </c>
+      <c r="F132" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="G132" s="8">
+        <v>1.36</v>
       </c>
       <c r="H132" s="9">
-        <v>0.79800000000000004</v>
+        <v>1</v>
       </c>
       <c r="I132" s="8">
-        <v>-3.85</v>
-      </c>
-      <c r="J132" s="10">
-        <v>61.4</v>
+        <v>25.4</v>
+      </c>
+      <c r="J132" s="8">
+        <v>39.6</v>
       </c>
       <c r="K132" s="9">
-        <v>7.92</v>
-      </c>
-      <c r="L132" s="10">
-        <v>45.6</v>
+        <v>8.92</v>
+      </c>
+      <c r="L132" s="8">
+        <v>44.9</v>
       </c>
       <c r="M132" s="9" t="s">
         <v>17</v>
@@ -8164,40 +8172,40 @@
     </row>
     <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>38261</v>
+        <v>38292</v>
       </c>
       <c r="B133" s="7">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="C133" s="7">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="D133" s="7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="E133" s="7">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="F133" s="8">
-        <v>-0.6</v>
+        <v>0.05</v>
       </c>
       <c r="G133" s="8">
-        <v>-5.17</v>
+        <v>0.45</v>
       </c>
       <c r="H133" s="9">
-        <v>0.83</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="I133" s="10">
-        <v>55.9</v>
-      </c>
-      <c r="J133" s="10">
-        <v>2.4</v>
+        <v>-3.85</v>
+      </c>
+      <c r="J133" s="8">
+        <v>61.4</v>
       </c>
       <c r="K133" s="9">
-        <v>7.12</v>
-      </c>
-      <c r="L133" s="10">
-        <v>44</v>
+        <v>7.92</v>
+      </c>
+      <c r="L133" s="8">
+        <v>45.6</v>
       </c>
       <c r="M133" s="9" t="s">
         <v>17</v>
@@ -8217,40 +8225,40 @@
     </row>
     <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>38231</v>
+        <v>38261</v>
       </c>
       <c r="B134" s="7">
-        <v>12.75</v>
+        <v>11.6</v>
       </c>
       <c r="C134" s="7">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="D134" s="7">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="E134" s="7">
-        <v>11.4</v>
-      </c>
-      <c r="F134" s="8">
-        <v>-1.1499999999999999</v>
-      </c>
-      <c r="G134" s="8">
-        <v>-9.02</v>
+        <v>11</v>
+      </c>
+      <c r="F134" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G134" s="10">
+        <v>-5.17</v>
       </c>
       <c r="H134" s="9">
-        <v>0.53200000000000003</v>
+        <v>0.83</v>
       </c>
       <c r="I134" s="8">
-        <v>-32.200000000000003</v>
-      </c>
-      <c r="J134" s="10">
-        <v>7.18</v>
+        <v>55.9</v>
+      </c>
+      <c r="J134" s="8">
+        <v>2.4</v>
       </c>
       <c r="K134" s="9">
-        <v>6.29</v>
-      </c>
-      <c r="L134" s="10">
-        <v>52.2</v>
+        <v>7.12</v>
+      </c>
+      <c r="L134" s="8">
+        <v>44</v>
       </c>
       <c r="M134" s="9" t="s">
         <v>17</v>
@@ -8270,40 +8278,40 @@
     </row>
     <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>38200</v>
+        <v>38231</v>
       </c>
       <c r="B135" s="7">
-        <v>14.8</v>
+        <v>12.75</v>
       </c>
       <c r="C135" s="7">
-        <v>12.75</v>
+        <v>11.6</v>
       </c>
       <c r="D135" s="7">
-        <v>15.1</v>
+        <v>12.3</v>
       </c>
       <c r="E135" s="7">
-        <v>11</v>
-      </c>
-      <c r="F135" s="8">
-        <v>-2.0499999999999998</v>
-      </c>
-      <c r="G135" s="8">
-        <v>-13.85</v>
+        <v>11.4</v>
+      </c>
+      <c r="F135" s="10">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="G135" s="10">
+        <v>-9.02</v>
       </c>
       <c r="H135" s="9">
-        <v>0.78400000000000003</v>
-      </c>
-      <c r="I135" s="8">
-        <v>-4.83</v>
-      </c>
-      <c r="J135" s="10">
-        <v>68.2</v>
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="I135" s="10">
+        <v>-32.200000000000003</v>
+      </c>
+      <c r="J135" s="8">
+        <v>7.18</v>
       </c>
       <c r="K135" s="9">
-        <v>5.76</v>
-      </c>
-      <c r="L135" s="10">
-        <v>58.3</v>
+        <v>6.29</v>
+      </c>
+      <c r="L135" s="8">
+        <v>52.2</v>
       </c>
       <c r="M135" s="9" t="s">
         <v>17</v>
@@ -8323,40 +8331,40 @@
     </row>
     <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>38169</v>
+        <v>38200</v>
       </c>
       <c r="B136" s="7">
-        <v>18.100000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="C136" s="7">
-        <v>14.8</v>
+        <v>12.75</v>
       </c>
       <c r="D136" s="7">
-        <v>18.100000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="E136" s="7">
-        <v>14.8</v>
-      </c>
-      <c r="F136" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="G136" s="8">
-        <v>-18.23</v>
+        <v>11</v>
+      </c>
+      <c r="F136" s="10">
+        <v>-2.0499999999999998</v>
+      </c>
+      <c r="G136" s="10">
+        <v>-13.85</v>
       </c>
       <c r="H136" s="9">
-        <v>0.82399999999999995</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="I136" s="10">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="J136" s="10">
-        <v>150.6</v>
+        <v>-4.83</v>
+      </c>
+      <c r="J136" s="8">
+        <v>68.2</v>
       </c>
       <c r="K136" s="9">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="L136" s="10">
-        <v>56.8</v>
+        <v>5.76</v>
+      </c>
+      <c r="L136" s="8">
+        <v>58.3</v>
       </c>
       <c r="M136" s="9" t="s">
         <v>17</v>
@@ -8376,40 +8384,40 @@
     </row>
     <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>38139</v>
+        <v>38169</v>
       </c>
       <c r="B137" s="7">
-        <v>18.899999999999999</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="C137" s="7">
-        <v>18.100000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="D137" s="7">
         <v>18.100000000000001</v>
       </c>
       <c r="E137" s="7">
-        <v>18</v>
-      </c>
-      <c r="F137" s="8">
-        <v>-0.8</v>
-      </c>
-      <c r="G137" s="8">
-        <v>-4.2300000000000004</v>
+        <v>14.8</v>
+      </c>
+      <c r="F137" s="10">
+        <v>-3.3</v>
+      </c>
+      <c r="G137" s="10">
+        <v>-18.23</v>
       </c>
       <c r="H137" s="9">
-        <v>0.80400000000000005</v>
-      </c>
-      <c r="I137" s="10">
-        <v>14.8</v>
-      </c>
-      <c r="J137" s="10">
-        <v>33.299999999999997</v>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="I137" s="8">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="J137" s="8">
+        <v>150.6</v>
       </c>
       <c r="K137" s="9">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="L137" s="10">
-        <v>46</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="L137" s="8">
+        <v>56.8</v>
       </c>
       <c r="M137" s="9" t="s">
         <v>17</v>
@@ -8429,40 +8437,40 @@
     </row>
     <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>38108</v>
+        <v>38139</v>
       </c>
       <c r="B138" s="7">
-        <v>20</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="C138" s="7">
-        <v>18.899999999999999</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="D138" s="7">
-        <v>20</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="E138" s="7">
-        <v>17</v>
-      </c>
-      <c r="F138" s="8">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="G138" s="8">
-        <v>-5.5</v>
+        <v>18</v>
+      </c>
+      <c r="F138" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G138" s="10">
+        <v>-4.2300000000000004</v>
       </c>
       <c r="H138" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="I138" s="10">
-        <v>6.2</v>
-      </c>
-      <c r="J138" s="10">
-        <v>49.7</v>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="I138" s="8">
+        <v>14.8</v>
+      </c>
+      <c r="J138" s="8">
+        <v>33.299999999999997</v>
       </c>
       <c r="K138" s="9">
-        <v>3.35</v>
-      </c>
-      <c r="L138" s="10">
-        <v>49.4</v>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="L138" s="8">
+        <v>46</v>
       </c>
       <c r="M138" s="9" t="s">
         <v>17</v>
@@ -8482,40 +8490,40 @@
     </row>
     <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>38078</v>
+        <v>38108</v>
       </c>
       <c r="B139" s="7">
         <v>20</v>
       </c>
       <c r="C139" s="7">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D139" s="7">
         <v>20</v>
       </c>
-      <c r="D139" s="7">
-        <v>21.5</v>
-      </c>
       <c r="E139" s="7">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="F139" s="9">
-        <v>0</v>
-      </c>
-      <c r="G139" s="9">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="F139" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G139" s="10">
+        <v>-5.5</v>
       </c>
       <c r="H139" s="9">
-        <v>0.65900000000000003</v>
+        <v>0.7</v>
       </c>
       <c r="I139" s="8">
-        <v>-20.2</v>
-      </c>
-      <c r="J139" s="10">
-        <v>9.7799999999999994</v>
+        <v>6.2</v>
+      </c>
+      <c r="J139" s="8">
+        <v>49.7</v>
       </c>
       <c r="K139" s="9">
-        <v>2.69</v>
-      </c>
-      <c r="L139" s="10">
-        <v>51.9</v>
+        <v>3.35</v>
+      </c>
+      <c r="L139" s="8">
+        <v>49.4</v>
       </c>
       <c r="M139" s="9" t="s">
         <v>17</v>
@@ -8535,40 +8543,40 @@
     </row>
     <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>38047</v>
+        <v>38078</v>
       </c>
       <c r="B140" s="7">
-        <v>21.9</v>
+        <v>20</v>
       </c>
       <c r="C140" s="7">
         <v>20</v>
       </c>
       <c r="D140" s="7">
-        <v>22.1</v>
+        <v>21.5</v>
       </c>
       <c r="E140" s="7">
-        <v>19.8</v>
-      </c>
-      <c r="F140" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="G140" s="8">
-        <v>-8.68</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F140" s="9">
+        <v>0</v>
+      </c>
+      <c r="G140" s="9">
+        <v>0</v>
       </c>
       <c r="H140" s="9">
-        <v>0.82599999999999996</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="I140" s="10">
-        <v>29.6</v>
-      </c>
-      <c r="J140" s="10">
-        <v>38.799999999999997</v>
+        <v>-20.2</v>
+      </c>
+      <c r="J140" s="8">
+        <v>9.7799999999999994</v>
       </c>
       <c r="K140" s="9">
-        <v>2.04</v>
-      </c>
-      <c r="L140" s="10">
-        <v>73.400000000000006</v>
+        <v>2.69</v>
+      </c>
+      <c r="L140" s="8">
+        <v>51.9</v>
       </c>
       <c r="M140" s="9" t="s">
         <v>17</v>
@@ -8588,40 +8596,40 @@
     </row>
     <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>38018</v>
+        <v>38047</v>
       </c>
       <c r="B141" s="7">
-        <v>23.5</v>
+        <v>21.9</v>
       </c>
       <c r="C141" s="7">
-        <v>21.9</v>
+        <v>20</v>
       </c>
       <c r="D141" s="7">
-        <v>23.6</v>
+        <v>22.1</v>
       </c>
       <c r="E141" s="7">
-        <v>21.9</v>
-      </c>
-      <c r="F141" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="G141" s="8">
-        <v>-6.81</v>
+        <v>19.8</v>
+      </c>
+      <c r="F141" s="10">
+        <v>-1.9</v>
+      </c>
+      <c r="G141" s="10">
+        <v>-8.68</v>
       </c>
       <c r="H141" s="9">
-        <v>0.63700000000000001</v>
-      </c>
-      <c r="I141" s="10">
-        <v>11.6</v>
-      </c>
-      <c r="J141" s="10">
-        <v>97.4</v>
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="I141" s="8">
+        <v>29.6</v>
+      </c>
+      <c r="J141" s="8">
+        <v>38.799999999999997</v>
       </c>
       <c r="K141" s="9">
-        <v>1.21</v>
-      </c>
-      <c r="L141" s="10">
-        <v>109.1</v>
+        <v>2.04</v>
+      </c>
+      <c r="L141" s="8">
+        <v>73.400000000000006</v>
       </c>
       <c r="M141" s="9" t="s">
         <v>17</v>
@@ -8641,40 +8649,40 @@
     </row>
     <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>37987</v>
+        <v>38018</v>
       </c>
       <c r="B142" s="7">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="C142" s="7">
-        <v>23.5</v>
+        <v>21.9</v>
       </c>
       <c r="D142" s="7">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="E142" s="7">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="F142" s="10">
-        <v>3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="G142" s="10">
-        <v>15.76</v>
+        <v>-6.81</v>
       </c>
       <c r="H142" s="9">
-        <v>0.57099999999999995</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="I142" s="8">
-        <v>-20.2</v>
-      </c>
-      <c r="J142" s="10">
-        <v>123.8</v>
+        <v>11.6</v>
+      </c>
+      <c r="J142" s="8">
+        <v>97.4</v>
       </c>
       <c r="K142" s="9">
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="L142" s="10">
-        <v>123.8</v>
+        <v>1.21</v>
+      </c>
+      <c r="L142" s="8">
+        <v>109.1</v>
       </c>
       <c r="M142" s="9" t="s">
         <v>17</v>
@@ -8694,40 +8702,40 @@
     </row>
     <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>37956</v>
+        <v>37987</v>
       </c>
       <c r="B143" s="7">
-        <v>17.100000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="C143" s="7">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="D143" s="7">
-        <v>20.3</v>
+        <v>23.7</v>
       </c>
       <c r="E143" s="7">
-        <v>17</v>
-      </c>
-      <c r="F143" s="10">
+        <v>22</v>
+      </c>
+      <c r="F143" s="8">
         <v>3.2</v>
       </c>
-      <c r="G143" s="10">
-        <v>18.71</v>
+      <c r="G143" s="8">
+        <v>15.76</v>
       </c>
       <c r="H143" s="9">
-        <v>0.71599999999999997</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="I143" s="10">
-        <v>45</v>
-      </c>
-      <c r="J143" s="10">
-        <v>51.5</v>
+        <v>-20.2</v>
+      </c>
+      <c r="J143" s="8">
+        <v>123.8</v>
       </c>
       <c r="K143" s="9">
-        <v>6.16</v>
-      </c>
-      <c r="L143" s="10">
-        <v>27.6</v>
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="L143" s="8">
+        <v>123.8</v>
       </c>
       <c r="M143" s="9" t="s">
         <v>17</v>
@@ -8747,40 +8755,40 @@
     </row>
     <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>37926</v>
+        <v>37956</v>
       </c>
       <c r="B144" s="7">
-        <v>16.3</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="C144" s="7">
-        <v>17.100000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="D144" s="7">
-        <v>17.600000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="E144" s="7">
-        <v>15.5</v>
-      </c>
-      <c r="F144" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="G144" s="10">
-        <v>4.91</v>
+        <v>17</v>
+      </c>
+      <c r="F144" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="G144" s="8">
+        <v>18.71</v>
       </c>
       <c r="H144" s="9">
-        <v>0.49399999999999999</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="I144" s="8">
-        <v>-39</v>
-      </c>
-      <c r="J144" s="10">
-        <v>13.7</v>
+        <v>45</v>
+      </c>
+      <c r="J144" s="8">
+        <v>51.5</v>
       </c>
       <c r="K144" s="9">
-        <v>5.44</v>
-      </c>
-      <c r="L144" s="10">
-        <v>25</v>
+        <v>6.16</v>
+      </c>
+      <c r="L144" s="8">
+        <v>27.6</v>
       </c>
       <c r="M144" s="9" t="s">
         <v>17</v>
@@ -8800,40 +8808,40 @@
     </row>
     <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>37895</v>
+        <v>37926</v>
       </c>
       <c r="B145" s="7">
-        <v>15.3</v>
+        <v>16.3</v>
       </c>
       <c r="C145" s="7">
-        <v>16.3</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="D145" s="7">
-        <v>16.5</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E145" s="7">
-        <v>15</v>
-      </c>
-      <c r="F145" s="10">
-        <v>1</v>
-      </c>
-      <c r="G145" s="10">
-        <v>6.54</v>
+        <v>15.5</v>
+      </c>
+      <c r="F145" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G145" s="8">
+        <v>4.91</v>
       </c>
       <c r="H145" s="9">
-        <v>0.81</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="I145" s="10">
-        <v>63.2</v>
-      </c>
-      <c r="J145" s="10">
-        <v>90.2</v>
+        <v>-39</v>
+      </c>
+      <c r="J145" s="8">
+        <v>13.7</v>
       </c>
       <c r="K145" s="9">
-        <v>4.95</v>
-      </c>
-      <c r="L145" s="10">
-        <v>26.3</v>
+        <v>5.44</v>
+      </c>
+      <c r="L145" s="8">
+        <v>25</v>
       </c>
       <c r="M145" s="9" t="s">
         <v>17</v>
@@ -8853,40 +8861,40 @@
     </row>
     <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>37865</v>
+        <v>37895</v>
       </c>
       <c r="B146" s="7">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="C146" s="7">
-        <v>15.3</v>
+        <v>16.3</v>
       </c>
       <c r="D146" s="7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="E146" s="7">
         <v>15</v>
       </c>
       <c r="F146" s="8">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="G146" s="8">
-        <v>-1.29</v>
+        <v>6.54</v>
       </c>
       <c r="H146" s="9">
-        <v>0.496</v>
-      </c>
-      <c r="I146" s="10">
-        <v>6.48</v>
-      </c>
-      <c r="J146" s="10">
-        <v>9.14</v>
+        <v>0.81</v>
+      </c>
+      <c r="I146" s="8">
+        <v>63.2</v>
+      </c>
+      <c r="J146" s="8">
+        <v>90.2</v>
       </c>
       <c r="K146" s="9">
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="L146" s="10">
-        <v>18.5</v>
+        <v>4.95</v>
+      </c>
+      <c r="L146" s="8">
+        <v>26.3</v>
       </c>
       <c r="M146" s="9" t="s">
         <v>17</v>
@@ -8906,40 +8914,40 @@
     </row>
     <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>37834</v>
+        <v>37865</v>
       </c>
       <c r="B147" s="7">
-        <v>11.8</v>
+        <v>15.5</v>
       </c>
       <c r="C147" s="7">
+        <v>15.3</v>
+      </c>
+      <c r="D147" s="7">
         <v>15.5</v>
       </c>
-      <c r="D147" s="7">
-        <v>16.5</v>
-      </c>
       <c r="E147" s="7">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="F147" s="10">
-        <v>3.7</v>
+        <v>-0.2</v>
       </c>
       <c r="G147" s="10">
-        <v>31.36</v>
+        <v>-1.29</v>
       </c>
       <c r="H147" s="9">
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="I147" s="10">
-        <v>41.7</v>
-      </c>
-      <c r="J147" s="10">
-        <v>7.93</v>
+        <v>0.496</v>
+      </c>
+      <c r="I147" s="8">
+        <v>6.48</v>
+      </c>
+      <c r="J147" s="8">
+        <v>9.14</v>
       </c>
       <c r="K147" s="9">
-        <v>3.64</v>
-      </c>
-      <c r="L147" s="10">
-        <v>19.899999999999999</v>
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L147" s="8">
+        <v>18.5</v>
       </c>
       <c r="M147" s="9" t="s">
         <v>17</v>
@@ -8959,40 +8967,40 @@
     </row>
     <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>37803</v>
+        <v>37834</v>
       </c>
       <c r="B148" s="7">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="C148" s="7">
-        <v>11.8</v>
+        <v>15.5</v>
       </c>
       <c r="D148" s="7">
-        <v>12.2</v>
+        <v>16.5</v>
       </c>
       <c r="E148" s="7">
-        <v>10</v>
-      </c>
-      <c r="F148" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="G148" s="10">
-        <v>8.26</v>
+        <v>11.6</v>
+      </c>
+      <c r="F148" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G148" s="8">
+        <v>31.36</v>
       </c>
       <c r="H148" s="9">
-        <v>0.32900000000000001</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="I148" s="8">
-        <v>-45.4</v>
+        <v>41.7</v>
       </c>
       <c r="J148" s="8">
-        <v>-11.9</v>
+        <v>7.93</v>
       </c>
       <c r="K148" s="9">
-        <v>3.17</v>
-      </c>
-      <c r="L148" s="10">
-        <v>21.8</v>
+        <v>3.64</v>
+      </c>
+      <c r="L148" s="8">
+        <v>19.899999999999999</v>
       </c>
       <c r="M148" s="9" t="s">
         <v>17</v>
@@ -9012,40 +9020,40 @@
     </row>
     <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>37773</v>
+        <v>37803</v>
       </c>
       <c r="B149" s="7">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="C149" s="7">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="D149" s="7">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="E149" s="7">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="F149" s="8">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="G149" s="8">
-        <v>-0.91</v>
+        <v>8.26</v>
       </c>
       <c r="H149" s="9">
-        <v>0.60299999999999998</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="I149" s="10">
-        <v>28.8</v>
+        <v>-45.4</v>
       </c>
       <c r="J149" s="10">
-        <v>26.6</v>
+        <v>-11.9</v>
       </c>
       <c r="K149" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="L149" s="10">
-        <v>27.5</v>
+        <v>3.17</v>
+      </c>
+      <c r="L149" s="8">
+        <v>21.8</v>
       </c>
       <c r="M149" s="9" t="s">
         <v>17</v>
@@ -9065,40 +9073,40 @@
     </row>
     <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>37742</v>
+        <v>37773</v>
       </c>
       <c r="B150" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C150" s="7">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D150" s="7">
         <v>11</v>
       </c>
       <c r="E150" s="7">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="F150" s="10">
-        <v>1</v>
+        <v>-0.1</v>
       </c>
       <c r="G150" s="10">
-        <v>10</v>
+        <v>-0.91</v>
       </c>
       <c r="H150" s="9">
-        <v>0.46800000000000003</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="I150" s="8">
-        <v>-22.1</v>
-      </c>
-      <c r="J150" s="10">
-        <v>0.57999999999999996</v>
+        <v>28.8</v>
+      </c>
+      <c r="J150" s="8">
+        <v>26.6</v>
       </c>
       <c r="K150" s="9">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="L150" s="10">
-        <v>27.7</v>
+        <v>2.84</v>
+      </c>
+      <c r="L150" s="8">
+        <v>27.5</v>
       </c>
       <c r="M150" s="9" t="s">
         <v>17</v>
@@ -9118,40 +9126,40 @@
     </row>
     <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>37712</v>
+        <v>37742</v>
       </c>
       <c r="B151" s="7">
         <v>10</v>
       </c>
       <c r="C151" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D151" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E151" s="7">
         <v>10</v>
       </c>
-      <c r="F151" s="9">
-        <v>0</v>
-      </c>
-      <c r="G151" s="9">
-        <v>0</v>
+      <c r="F151" s="8">
+        <v>1</v>
+      </c>
+      <c r="G151" s="8">
+        <v>10</v>
       </c>
       <c r="H151" s="9">
-        <v>0.60099999999999998</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="I151" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="J151" s="10">
-        <v>64.099999999999994</v>
+        <v>-22.1</v>
+      </c>
+      <c r="J151" s="8">
+        <v>0.57999999999999996</v>
       </c>
       <c r="K151" s="9">
-        <v>1.77</v>
-      </c>
-      <c r="L151" s="10">
-        <v>37.5</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="L151" s="8">
+        <v>27.7</v>
       </c>
       <c r="M151" s="9" t="s">
         <v>17</v>
@@ -9171,7 +9179,7 @@
     </row>
     <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>37681</v>
+        <v>37712</v>
       </c>
       <c r="B152" s="7">
         <v>10</v>
@@ -9192,19 +9200,19 @@
         <v>0</v>
       </c>
       <c r="H152" s="9">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="I152" s="10">
-        <v>82.4</v>
-      </c>
-      <c r="J152" s="10">
-        <v>62</v>
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="I152" s="8">
+        <v>0.87</v>
+      </c>
+      <c r="J152" s="8">
+        <v>64.099999999999994</v>
       </c>
       <c r="K152" s="9">
-        <v>1.17</v>
-      </c>
-      <c r="L152" s="10">
-        <v>27</v>
+        <v>1.77</v>
+      </c>
+      <c r="L152" s="8">
+        <v>37.5</v>
       </c>
       <c r="M152" s="9" t="s">
         <v>17</v>
@@ -9224,40 +9232,40 @@
     </row>
     <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>37653</v>
+        <v>37681</v>
       </c>
       <c r="B153" s="7">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="C153" s="7">
         <v>10</v>
       </c>
       <c r="D153" s="7">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="E153" s="7">
         <v>10</v>
       </c>
-      <c r="F153" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G153" s="8">
-        <v>-20</v>
+      <c r="F153" s="9">
+        <v>0</v>
+      </c>
+      <c r="G153" s="9">
+        <v>0</v>
       </c>
       <c r="H153" s="9">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="I153" s="10">
-        <v>27.9</v>
-      </c>
-      <c r="J153" s="10">
-        <v>39.799999999999997</v>
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="I153" s="8">
+        <v>82.4</v>
+      </c>
+      <c r="J153" s="8">
+        <v>62</v>
       </c>
       <c r="K153" s="9">
-        <v>0.57799999999999996</v>
-      </c>
-      <c r="L153" s="10">
-        <v>3.87</v>
+        <v>1.17</v>
+      </c>
+      <c r="L153" s="8">
+        <v>27</v>
       </c>
       <c r="M153" s="9" t="s">
         <v>17</v>
@@ -9277,54 +9285,107 @@
     </row>
     <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>37622</v>
+        <v>37653</v>
       </c>
       <c r="B154" s="7">
         <v>12.5</v>
       </c>
       <c r="C154" s="7">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="D154" s="7">
         <v>12.5</v>
       </c>
       <c r="E154" s="7">
+        <v>10</v>
+      </c>
+      <c r="F154" s="10">
+        <v>-2.5</v>
+      </c>
+      <c r="G154" s="10">
+        <v>-20</v>
+      </c>
+      <c r="H154" s="9">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="I154" s="8">
+        <v>27.9</v>
+      </c>
+      <c r="J154" s="8">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="K154" s="9">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="L154" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="M154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q154" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>37622</v>
+      </c>
+      <c r="B155" s="7">
         <v>12.5</v>
       </c>
-      <c r="F154" s="9">
+      <c r="C155" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="D155" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="E155" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="F155" s="9">
         <v>0</v>
       </c>
-      <c r="G154" s="9">
+      <c r="G155" s="9">
         <v>0</v>
       </c>
-      <c r="H154" s="9">
+      <c r="H155" s="9">
         <v>0.255</v>
       </c>
-      <c r="I154" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J154" s="8">
+      <c r="I155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J155" s="10">
         <v>-21</v>
       </c>
-      <c r="K154" s="9">
+      <c r="K155" s="9">
         <v>0.255</v>
       </c>
-      <c r="L154" s="8">
+      <c r="L155" s="10">
         <v>-21</v>
       </c>
-      <c r="M154" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N154" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O154" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P154" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q154" s="9" t="s">
+      <c r="M155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q155" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9343,7 +9404,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>